--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30092D8E-7503-4129-8B97-BD2E0B0D8606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4B84F1-AECA-464C-952B-21D61A76026F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$231</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="233">
   <si>
     <t>LP</t>
   </si>
@@ -67,111 +67,21 @@
     <t>LP-050565</t>
   </si>
   <si>
-    <t>LP-050631</t>
-  </si>
-  <si>
-    <t>LP-050632</t>
-  </si>
-  <si>
-    <t>LP-050633</t>
-  </si>
-  <si>
-    <t>LP-050635</t>
-  </si>
-  <si>
-    <t>LP-050827</t>
-  </si>
-  <si>
-    <t>LP-050839</t>
-  </si>
-  <si>
-    <t>LP-050858</t>
-  </si>
-  <si>
-    <t>LP-050859</t>
-  </si>
-  <si>
-    <t>LP-050873</t>
-  </si>
-  <si>
-    <t>LP-050929</t>
-  </si>
-  <si>
-    <t>LP-050956</t>
-  </si>
-  <si>
     <t>LP-050958</t>
   </si>
   <si>
-    <t>LP-050986</t>
-  </si>
-  <si>
-    <t>LP-051060</t>
-  </si>
-  <si>
-    <t>LP-051094</t>
-  </si>
-  <si>
-    <t>LP-051112</t>
-  </si>
-  <si>
-    <t>LP-051163</t>
-  </si>
-  <si>
-    <t>LP-051230</t>
-  </si>
-  <si>
-    <t>LP-051231</t>
-  </si>
-  <si>
-    <t>LP-051270</t>
-  </si>
-  <si>
-    <t>LP-051357</t>
-  </si>
-  <si>
-    <t>LP-051400</t>
-  </si>
-  <si>
-    <t>LP-051406</t>
-  </si>
-  <si>
-    <t>LP-051455</t>
-  </si>
-  <si>
-    <t>LP-051456</t>
-  </si>
-  <si>
-    <t>LP-051484</t>
+    <t>Compromisso pendente!</t>
   </si>
   <si>
     <t>LP-051570</t>
   </si>
   <si>
-    <t>LP-051592</t>
-  </si>
-  <si>
     <t>LP-051629</t>
   </si>
   <si>
-    <t>LP-051662</t>
-  </si>
-  <si>
-    <t>LP-051666</t>
-  </si>
-  <si>
-    <t>LP-051667</t>
-  </si>
-  <si>
     <t>LP-051684</t>
   </si>
   <si>
-    <t>LP-051747</t>
-  </si>
-  <si>
-    <t>LP-051844</t>
-  </si>
-  <si>
     <t>LP-051845</t>
   </si>
   <si>
@@ -181,175 +91,25 @@
     <t>LP-051847</t>
   </si>
   <si>
-    <t>LP-051855</t>
-  </si>
-  <si>
-    <t>LP-051857</t>
-  </si>
-  <si>
     <t>LP-051859</t>
   </si>
   <si>
-    <t>LP-051861</t>
-  </si>
-  <si>
     <t>LP-051865</t>
   </si>
   <si>
     <t>LP-051866</t>
   </si>
   <si>
-    <t>LP-051871</t>
-  </si>
-  <si>
-    <t>LP-051901</t>
-  </si>
-  <si>
-    <t>LP-051919</t>
-  </si>
-  <si>
     <t>LP-051931</t>
   </si>
   <si>
-    <t>LP-052006</t>
-  </si>
-  <si>
-    <t>LP-052007</t>
-  </si>
-  <si>
-    <t>LP-052019</t>
-  </si>
-  <si>
-    <t>LP-052021</t>
-  </si>
-  <si>
-    <t>LP-052083</t>
-  </si>
-  <si>
-    <t>LP-052086</t>
-  </si>
-  <si>
-    <t>LP-052094</t>
-  </si>
-  <si>
-    <t>LP-052095</t>
-  </si>
-  <si>
-    <t>LP-052166</t>
-  </si>
-  <si>
-    <t>LP-052197</t>
-  </si>
-  <si>
-    <t>LP-052211</t>
-  </si>
-  <si>
-    <t>LP-052295</t>
-  </si>
-  <si>
-    <t>LP-052299</t>
-  </si>
-  <si>
-    <t>LP-033611</t>
-  </si>
-  <si>
-    <t>LP-040735</t>
-  </si>
-  <si>
-    <t>LP-043162</t>
-  </si>
-  <si>
-    <t>LP-043280</t>
-  </si>
-  <si>
-    <t>LP-043975</t>
-  </si>
-  <si>
-    <t>LP-044234</t>
-  </si>
-  <si>
-    <t>LP-045835</t>
-  </si>
-  <si>
-    <t>LP-045874</t>
-  </si>
-  <si>
-    <t>LP-045877</t>
-  </si>
-  <si>
     <t>LP-046519</t>
   </si>
   <si>
-    <t>LP-046966</t>
-  </si>
-  <si>
-    <t>LP-047977</t>
-  </si>
-  <si>
-    <t>LP-047988</t>
-  </si>
-  <si>
-    <t>LP-048161</t>
-  </si>
-  <si>
-    <t>LP-048171</t>
-  </si>
-  <si>
-    <t>LP-048177</t>
-  </si>
-  <si>
-    <t>LP-048357</t>
-  </si>
-  <si>
-    <t>LP-048362</t>
-  </si>
-  <si>
-    <t>LP-049234</t>
-  </si>
-  <si>
-    <t>LP-049329</t>
-  </si>
-  <si>
-    <t>LP-049973</t>
-  </si>
-  <si>
-    <t>LP-050406</t>
-  </si>
-  <si>
-    <t>LP-050453</t>
-  </si>
-  <si>
-    <t>LP-050457</t>
-  </si>
-  <si>
-    <t>LP-050517</t>
-  </si>
-  <si>
     <t>LP-050538</t>
   </si>
   <si>
     <t>LP-050608</t>
-  </si>
-  <si>
-    <t>LP-050765</t>
-  </si>
-  <si>
-    <t>LP-050766</t>
-  </si>
-  <si>
-    <t>LP-050782</t>
-  </si>
-  <si>
-    <t>LP-050837</t>
-  </si>
-  <si>
-    <t>LP-050860</t>
-  </si>
-  <si>
-    <t>LP-050868</t>
-  </si>
-  <si>
-    <t>LP-050869</t>
   </si>
   <si>
     <t>LP-050918</t>
@@ -1324,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B313"/>
+  <dimension ref="A1:B231"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1407,850 +1167,898 @@
       <c r="A10" t="s">
         <v>11</v>
       </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>179</v>
+        <v>26</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
@@ -2511,416 +2319,6 @@
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4B84F1-AECA-464C-952B-21D61A76026F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975625C3-9456-45D7-8719-BB7340AFAC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$160</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="162">
   <si>
     <t>LP</t>
   </si>
@@ -103,469 +103,256 @@
     <t>LP-051931</t>
   </si>
   <si>
+    <t>LP-050538</t>
+  </si>
+  <si>
+    <t>LP-050608</t>
+  </si>
+  <si>
+    <t>LP-051375</t>
+  </si>
+  <si>
+    <t>LP-051409</t>
+  </si>
+  <si>
+    <t>LP-051498</t>
+  </si>
+  <si>
+    <t>LP-051501</t>
+  </si>
+  <si>
+    <t>LP-051502</t>
+  </si>
+  <si>
+    <t>LP-051506</t>
+  </si>
+  <si>
+    <t>LP-051507</t>
+  </si>
+  <si>
+    <t>LP-051601</t>
+  </si>
+  <si>
+    <t>LP-051603</t>
+  </si>
+  <si>
+    <t>LP-051604</t>
+  </si>
+  <si>
+    <t>LP-051605</t>
+  </si>
+  <si>
+    <t>LP-051664</t>
+  </si>
+  <si>
+    <t>LP-051665</t>
+  </si>
+  <si>
+    <t>LP-051485</t>
+  </si>
+  <si>
+    <t>LP-047840</t>
+  </si>
+  <si>
+    <t>LP-048259</t>
+  </si>
+  <si>
+    <t>LP-048389</t>
+  </si>
+  <si>
+    <t>LP-048982</t>
+  </si>
+  <si>
+    <t>LP-049000</t>
+  </si>
+  <si>
+    <t>LP-049035</t>
+  </si>
+  <si>
+    <t>LP-049119</t>
+  </si>
+  <si>
+    <t>LP-049142</t>
+  </si>
+  <si>
+    <t>LP-049162</t>
+  </si>
+  <si>
+    <t>LP-049333</t>
+  </si>
+  <si>
+    <t>LP-049343</t>
+  </si>
+  <si>
+    <t>LP-049347</t>
+  </si>
+  <si>
+    <t>LP-049359</t>
+  </si>
+  <si>
+    <t>LP-049375</t>
+  </si>
+  <si>
+    <t>LP-049383</t>
+  </si>
+  <si>
+    <t>LP-049465</t>
+  </si>
+  <si>
+    <t>LP-049507</t>
+  </si>
+  <si>
+    <t>LP-049663</t>
+  </si>
+  <si>
+    <t>LP-049664</t>
+  </si>
+  <si>
+    <t>LP-049667</t>
+  </si>
+  <si>
+    <t>LP-049771</t>
+  </si>
+  <si>
+    <t>LP-049772</t>
+  </si>
+  <si>
+    <t>LP-049850</t>
+  </si>
+  <si>
+    <t>LP-549852</t>
+  </si>
+  <si>
+    <t>LP-049969</t>
+  </si>
+  <si>
+    <t>LP-049970</t>
+  </si>
+  <si>
+    <t>LP-050125</t>
+  </si>
+  <si>
+    <t>LP-050155</t>
+  </si>
+  <si>
+    <t>LP-050256</t>
+  </si>
+  <si>
+    <t>LP-050276</t>
+  </si>
+  <si>
+    <t>LP-050393</t>
+  </si>
+  <si>
+    <t>LP-050402</t>
+  </si>
+  <si>
+    <t>LP-050414</t>
+  </si>
+  <si>
+    <t>LP-050434</t>
+  </si>
+  <si>
+    <t>LP-050437</t>
+  </si>
+  <si>
+    <t>LP-050471</t>
+  </si>
+  <si>
+    <t>LP-050719</t>
+  </si>
+  <si>
+    <t>LP-050721</t>
+  </si>
+  <si>
+    <t>LP-050749</t>
+  </si>
+  <si>
+    <t>LP-050751</t>
+  </si>
+  <si>
+    <t>LP-050867</t>
+  </si>
+  <si>
+    <t>LP-051076</t>
+  </si>
+  <si>
+    <t>LP-051078</t>
+  </si>
+  <si>
+    <t>LP-051081</t>
+  </si>
+  <si>
+    <t>LP-051084</t>
+  </si>
+  <si>
+    <t>LP-051087</t>
+  </si>
+  <si>
+    <t>LP-051138</t>
+  </si>
+  <si>
+    <t>LP-051157</t>
+  </si>
+  <si>
+    <t>LP-051158</t>
+  </si>
+  <si>
+    <t>LP-051256</t>
+  </si>
+  <si>
+    <t>LP-051282</t>
+  </si>
+  <si>
+    <t>LP-051283</t>
+  </si>
+  <si>
+    <t>LP-051300</t>
+  </si>
+  <si>
+    <t>LP-051301</t>
+  </si>
+  <si>
+    <t>LP-051423</t>
+  </si>
+  <si>
+    <t>LP-051492</t>
+  </si>
+  <si>
+    <t>LP-051520</t>
+  </si>
+  <si>
+    <t>LP-051522</t>
+  </si>
+  <si>
+    <t>LP-051539</t>
+  </si>
+  <si>
+    <t>LP-051545</t>
+  </si>
+  <si>
+    <t>LP-051718</t>
+  </si>
+  <si>
+    <t>LP-051719</t>
+  </si>
+  <si>
+    <t>LP-051728</t>
+  </si>
+  <si>
+    <t>LP-051729</t>
+  </si>
+  <si>
+    <t>LP-052098</t>
+  </si>
+  <si>
+    <t>LP-044462</t>
+  </si>
+  <si>
+    <t>LP-045222</t>
+  </si>
+  <si>
     <t>LP-046519</t>
-  </si>
-  <si>
-    <t>LP-050538</t>
-  </si>
-  <si>
-    <t>LP-050608</t>
-  </si>
-  <si>
-    <t>LP-050918</t>
-  </si>
-  <si>
-    <t>LP-050973</t>
-  </si>
-  <si>
-    <t>LP-050977</t>
-  </si>
-  <si>
-    <t>LP-050987</t>
-  </si>
-  <si>
-    <t>LP-050988</t>
-  </si>
-  <si>
-    <t>LP-051014</t>
-  </si>
-  <si>
-    <t>LP-051015</t>
-  </si>
-  <si>
-    <t>LP-051090</t>
-  </si>
-  <si>
-    <t>LP-051092</t>
-  </si>
-  <si>
-    <t>LP-051108</t>
-  </si>
-  <si>
-    <t>LP-051113</t>
-  </si>
-  <si>
-    <t>LP-051126</t>
-  </si>
-  <si>
-    <t>LP-051165</t>
-  </si>
-  <si>
-    <t>LP-051212</t>
-  </si>
-  <si>
-    <t>LP-051227</t>
-  </si>
-  <si>
-    <t>LP-051234</t>
-  </si>
-  <si>
-    <t>LP-051236</t>
-  </si>
-  <si>
-    <t>LP-051358</t>
-  </si>
-  <si>
-    <t>LP-051375</t>
-  </si>
-  <si>
-    <t>LP-051409</t>
-  </si>
-  <si>
-    <t>LP-051498</t>
-  </si>
-  <si>
-    <t>LP-051501</t>
-  </si>
-  <si>
-    <t>LP-051502</t>
-  </si>
-  <si>
-    <t>LP-051506</t>
-  </si>
-  <si>
-    <t>LP-051507</t>
-  </si>
-  <si>
-    <t>LP-051524</t>
-  </si>
-  <si>
-    <t>LP-051601</t>
-  </si>
-  <si>
-    <t>LP-051603</t>
-  </si>
-  <si>
-    <t>LP-051604</t>
-  </si>
-  <si>
-    <t>LP-051605</t>
-  </si>
-  <si>
-    <t>LP-051646</t>
-  </si>
-  <si>
-    <t>LP-051647</t>
-  </si>
-  <si>
-    <t>LP-051648</t>
-  </si>
-  <si>
-    <t>LP-051649</t>
-  </si>
-  <si>
-    <t>LP-051650</t>
-  </si>
-  <si>
-    <t>LP-051651</t>
-  </si>
-  <si>
-    <t>LP-051652</t>
-  </si>
-  <si>
-    <t>LP-051653</t>
-  </si>
-  <si>
-    <t>LP-051654</t>
-  </si>
-  <si>
-    <t>LP-051655</t>
-  </si>
-  <si>
-    <t>LP-051664</t>
-  </si>
-  <si>
-    <t>LP-051665</t>
-  </si>
-  <si>
-    <t>LP-051886</t>
-  </si>
-  <si>
-    <t>LP-051893</t>
-  </si>
-  <si>
-    <t>LP-051918</t>
-  </si>
-  <si>
-    <t>LP-052037</t>
-  </si>
-  <si>
-    <t>LP-052348</t>
-  </si>
-  <si>
-    <t>LP-052349</t>
-  </si>
-  <si>
-    <t>LP-052354</t>
-  </si>
-  <si>
-    <t>LP-052392</t>
-  </si>
-  <si>
-    <t>LP-052444</t>
-  </si>
-  <si>
-    <t>LP-052466</t>
-  </si>
-  <si>
-    <t>LP-040674</t>
-  </si>
-  <si>
-    <t>LP-046158</t>
-  </si>
-  <si>
-    <t>LP-047205</t>
-  </si>
-  <si>
-    <t>LP-049046</t>
-  </si>
-  <si>
-    <t>LP-049350</t>
-  </si>
-  <si>
-    <t>LP-049758</t>
-  </si>
-  <si>
-    <t>LP-049963</t>
-  </si>
-  <si>
-    <t>LP-050031</t>
-  </si>
-  <si>
-    <t>LP-050095</t>
-  </si>
-  <si>
-    <t>LP-050407</t>
-  </si>
-  <si>
-    <t>LP-050415</t>
-  </si>
-  <si>
-    <t>LP-050667</t>
-  </si>
-  <si>
-    <t>LP-050729</t>
-  </si>
-  <si>
-    <t>LP-051036</t>
-  </si>
-  <si>
-    <t>LP-051067</t>
-  </si>
-  <si>
-    <t>LP-051077</t>
-  </si>
-  <si>
-    <t>LP-051080</t>
-  </si>
-  <si>
-    <t>LP-051082</t>
-  </si>
-  <si>
-    <t>LP-051083</t>
-  </si>
-  <si>
-    <t>LP-051159</t>
-  </si>
-  <si>
-    <t>LP-051160</t>
-  </si>
-  <si>
-    <t>LP-051379</t>
-  </si>
-  <si>
-    <t>LP-051385</t>
-  </si>
-  <si>
-    <t>LP-051386</t>
-  </si>
-  <si>
-    <t>LP-051422</t>
-  </si>
-  <si>
-    <t>LP-051428</t>
-  </si>
-  <si>
-    <t>LP-051485</t>
-  </si>
-  <si>
-    <t>LP-052188</t>
-  </si>
-  <si>
-    <t>LP-044816</t>
-  </si>
-  <si>
-    <t>LP-045910</t>
-  </si>
-  <si>
-    <t>LP-046171</t>
-  </si>
-  <si>
-    <t>LP-046811</t>
-  </si>
-  <si>
-    <t>LP-047333</t>
-  </si>
-  <si>
-    <t>LP-047840</t>
-  </si>
-  <si>
-    <t>LP-048259</t>
-  </si>
-  <si>
-    <t>LP-048389</t>
-  </si>
-  <si>
-    <t>LP-048982</t>
-  </si>
-  <si>
-    <t>LP-049000</t>
-  </si>
-  <si>
-    <t>LP-049035</t>
-  </si>
-  <si>
-    <t>LP-049119</t>
-  </si>
-  <si>
-    <t>LP-049142</t>
-  </si>
-  <si>
-    <t>LP-049162</t>
-  </si>
-  <si>
-    <t>LP-049333</t>
-  </si>
-  <si>
-    <t>LP-049343</t>
-  </si>
-  <si>
-    <t>LP-049347</t>
-  </si>
-  <si>
-    <t>LP-049359</t>
-  </si>
-  <si>
-    <t>LP-049375</t>
-  </si>
-  <si>
-    <t>LP-049383</t>
-  </si>
-  <si>
-    <t>LP-049465</t>
-  </si>
-  <si>
-    <t>LP-049507</t>
-  </si>
-  <si>
-    <t>LP-049663</t>
-  </si>
-  <si>
-    <t>LP-049664</t>
-  </si>
-  <si>
-    <t>LP-049667</t>
-  </si>
-  <si>
-    <t>LP-049771</t>
-  </si>
-  <si>
-    <t>LP-049772</t>
-  </si>
-  <si>
-    <t>LP-049850</t>
-  </si>
-  <si>
-    <t>LP-549852</t>
-  </si>
-  <si>
-    <t>LP-049969</t>
-  </si>
-  <si>
-    <t>LP-049970</t>
-  </si>
-  <si>
-    <t>LP-050125</t>
-  </si>
-  <si>
-    <t>LP-050155</t>
-  </si>
-  <si>
-    <t>LP-050256</t>
-  </si>
-  <si>
-    <t>LP-050276</t>
-  </si>
-  <si>
-    <t>LP-050393</t>
-  </si>
-  <si>
-    <t>LP-050402</t>
-  </si>
-  <si>
-    <t>LP-050414</t>
-  </si>
-  <si>
-    <t>LP-050434</t>
-  </si>
-  <si>
-    <t>LP-050437</t>
-  </si>
-  <si>
-    <t>LP-050471</t>
-  </si>
-  <si>
-    <t>LP-050719</t>
-  </si>
-  <si>
-    <t>LP-050721</t>
-  </si>
-  <si>
-    <t>LP-050749</t>
-  </si>
-  <si>
-    <t>LP-050751</t>
-  </si>
-  <si>
-    <t>LP-050867</t>
-  </si>
-  <si>
-    <t>LP-051076</t>
-  </si>
-  <si>
-    <t>LP-051078</t>
-  </si>
-  <si>
-    <t>LP-051081</t>
-  </si>
-  <si>
-    <t>LP-051084</t>
-  </si>
-  <si>
-    <t>LP-051087</t>
-  </si>
-  <si>
-    <t>LP-051138</t>
-  </si>
-  <si>
-    <t>LP-051157</t>
-  </si>
-  <si>
-    <t>LP-051158</t>
-  </si>
-  <si>
-    <t>LP-051256</t>
-  </si>
-  <si>
-    <t>LP-051282</t>
-  </si>
-  <si>
-    <t>LP-051283</t>
-  </si>
-  <si>
-    <t>LP-051300</t>
-  </si>
-  <si>
-    <t>LP-051301</t>
-  </si>
-  <si>
-    <t>LP-051423</t>
-  </si>
-  <si>
-    <t>LP-051492</t>
-  </si>
-  <si>
-    <t>LP-051520</t>
-  </si>
-  <si>
-    <t>LP-051522</t>
-  </si>
-  <si>
-    <t>LP-051539</t>
-  </si>
-  <si>
-    <t>LP-051545</t>
-  </si>
-  <si>
-    <t>LP-051718</t>
-  </si>
-  <si>
-    <t>LP-051719</t>
-  </si>
-  <si>
-    <t>LP-051728</t>
-  </si>
-  <si>
-    <t>LP-051729</t>
-  </si>
-  <si>
-    <t>LP-052098</t>
-  </si>
-  <si>
-    <t>LP-044462</t>
-  </si>
-  <si>
-    <t>LP-045222</t>
   </si>
   <si>
     <t>LP-047092</t>
@@ -1084,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B231"/>
+  <dimension ref="A1:B160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1277,7 +1064,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -1285,7 +1072,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
@@ -1293,1032 +1080,719 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975625C3-9456-45D7-8719-BB7340AFAC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970D4AAC-166E-45E1-8E63-6402194AF8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$89</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
   <si>
     <t>LP</t>
   </si>
@@ -151,232 +151,25 @@
     <t>LP-051485</t>
   </si>
   <si>
-    <t>LP-047840</t>
-  </si>
-  <si>
-    <t>LP-048259</t>
-  </si>
-  <si>
     <t>LP-048389</t>
   </si>
   <si>
     <t>LP-048982</t>
   </si>
   <si>
-    <t>LP-049000</t>
-  </si>
-  <si>
-    <t>LP-049035</t>
-  </si>
-  <si>
-    <t>LP-049119</t>
-  </si>
-  <si>
-    <t>LP-049142</t>
-  </si>
-  <si>
-    <t>LP-049162</t>
-  </si>
-  <si>
-    <t>LP-049333</t>
-  </si>
-  <si>
-    <t>LP-049343</t>
-  </si>
-  <si>
-    <t>LP-049347</t>
-  </si>
-  <si>
-    <t>LP-049359</t>
-  </si>
-  <si>
-    <t>LP-049375</t>
-  </si>
-  <si>
-    <t>LP-049383</t>
-  </si>
-  <si>
-    <t>LP-049465</t>
-  </si>
-  <si>
-    <t>LP-049507</t>
-  </si>
-  <si>
-    <t>LP-049663</t>
-  </si>
-  <si>
-    <t>LP-049664</t>
-  </si>
-  <si>
-    <t>LP-049667</t>
-  </si>
-  <si>
-    <t>LP-049771</t>
-  </si>
-  <si>
-    <t>LP-049772</t>
-  </si>
-  <si>
-    <t>LP-049850</t>
-  </si>
-  <si>
     <t>LP-549852</t>
   </si>
   <si>
-    <t>LP-049969</t>
-  </si>
-  <si>
-    <t>LP-049970</t>
-  </si>
-  <si>
-    <t>LP-050125</t>
-  </si>
-  <si>
-    <t>LP-050155</t>
-  </si>
-  <si>
-    <t>LP-050256</t>
+    <t>LP não existe!</t>
   </si>
   <si>
     <t>LP-050276</t>
   </si>
   <si>
-    <t>LP-050393</t>
-  </si>
-  <si>
-    <t>LP-050402</t>
-  </si>
-  <si>
-    <t>LP-050414</t>
-  </si>
-  <si>
-    <t>LP-050434</t>
-  </si>
-  <si>
-    <t>LP-050437</t>
-  </si>
-  <si>
-    <t>LP-050471</t>
-  </si>
-  <si>
     <t>LP-050719</t>
   </si>
   <si>
-    <t>LP-050721</t>
-  </si>
-  <si>
-    <t>LP-050749</t>
-  </si>
-  <si>
-    <t>LP-050751</t>
-  </si>
-  <si>
-    <t>LP-050867</t>
-  </si>
-  <si>
-    <t>LP-051076</t>
-  </si>
-  <si>
-    <t>LP-051078</t>
-  </si>
-  <si>
-    <t>LP-051081</t>
-  </si>
-  <si>
-    <t>LP-051084</t>
-  </si>
-  <si>
-    <t>LP-051087</t>
-  </si>
-  <si>
-    <t>LP-051138</t>
-  </si>
-  <si>
-    <t>LP-051157</t>
-  </si>
-  <si>
-    <t>LP-051158</t>
-  </si>
-  <si>
-    <t>LP-051256</t>
-  </si>
-  <si>
-    <t>LP-051282</t>
-  </si>
-  <si>
-    <t>LP-051283</t>
-  </si>
-  <si>
-    <t>LP-051300</t>
-  </si>
-  <si>
-    <t>LP-051301</t>
-  </si>
-  <si>
-    <t>LP-051423</t>
-  </si>
-  <si>
-    <t>LP-051492</t>
-  </si>
-  <si>
-    <t>LP-051520</t>
-  </si>
-  <si>
-    <t>LP-051522</t>
-  </si>
-  <si>
-    <t>LP-051539</t>
-  </si>
-  <si>
-    <t>LP-051545</t>
-  </si>
-  <si>
-    <t>LP-051718</t>
-  </si>
-  <si>
-    <t>LP-051719</t>
-  </si>
-  <si>
-    <t>LP-051728</t>
-  </si>
-  <si>
-    <t>LP-051729</t>
-  </si>
-  <si>
     <t>LP-052098</t>
-  </si>
-  <si>
-    <t>LP-044462</t>
-  </si>
-  <si>
-    <t>LP-045222</t>
-  </si>
-  <si>
-    <t>LP-046519</t>
-  </si>
-  <si>
-    <t>LP-047092</t>
-  </si>
-  <si>
-    <t>LP-047257</t>
-  </si>
-  <si>
-    <t>LP-047258</t>
-  </si>
-  <si>
-    <t>LP-047283</t>
-  </si>
-  <si>
-    <t>LP-047287</t>
-  </si>
-  <si>
-    <t>LP-047294</t>
-  </si>
-  <si>
-    <t>LP-047454</t>
-  </si>
-  <si>
-    <t>LP-047549</t>
   </si>
   <si>
     <t>LP-047778</t>
@@ -871,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B160"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1194,605 +987,268 @@
       <c r="A40" t="s">
         <v>42</v>
       </c>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
+      <c r="B42" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970D4AAC-166E-45E1-8E63-6402194AF8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB74030A-5DCA-493C-96EC-1EFA5C812C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$49</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="53">
   <si>
     <t>LP</t>
   </si>
@@ -172,136 +172,16 @@
     <t>LP-052098</t>
   </si>
   <si>
-    <t>LP-047778</t>
-  </si>
-  <si>
-    <t>LP-047989</t>
-  </si>
-  <si>
-    <t>LP-047991</t>
-  </si>
-  <si>
-    <t>LP-048010</t>
-  </si>
-  <si>
-    <t>LP-048343</t>
-  </si>
-  <si>
-    <t>LP-048351</t>
-  </si>
-  <si>
-    <t>LP-048397</t>
-  </si>
-  <si>
-    <t>LP-048426</t>
-  </si>
-  <si>
-    <t>LP-049431</t>
-  </si>
-  <si>
-    <t>LP-050098</t>
-  </si>
-  <si>
-    <t>LP-050137</t>
-  </si>
-  <si>
-    <t>LP-050248</t>
-  </si>
-  <si>
-    <t>LP-050310</t>
-  </si>
-  <si>
-    <t>LP-050445</t>
-  </si>
-  <si>
-    <t>LP-050895</t>
-  </si>
-  <si>
-    <t>LP-051011</t>
-  </si>
-  <si>
-    <t>LP-051095</t>
-  </si>
-  <si>
-    <t>LP-051172</t>
-  </si>
-  <si>
-    <t>LP-051224</t>
-  </si>
-  <si>
-    <t>LP-051318</t>
-  </si>
-  <si>
-    <t>LP-051319</t>
-  </si>
-  <si>
-    <t>LP-051383</t>
-  </si>
-  <si>
-    <t>LP-051436</t>
-  </si>
-  <si>
     <t>LP-051626</t>
   </si>
   <si>
     <t>LP-051658</t>
   </si>
   <si>
-    <t>LP-051663</t>
-  </si>
-  <si>
     <t>LP-051756</t>
   </si>
   <si>
-    <t>LP-051775</t>
-  </si>
-  <si>
-    <t>LP-051938</t>
-  </si>
-  <si>
-    <t>LP-051967</t>
-  </si>
-  <si>
-    <t>LP-052088</t>
-  </si>
-  <si>
-    <t>LP-052110</t>
-  </si>
-  <si>
-    <t>LP-052133</t>
-  </si>
-  <si>
-    <t>LP-052155</t>
-  </si>
-  <si>
-    <t>LP-052192</t>
-  </si>
-  <si>
-    <t>LP-052253</t>
-  </si>
-  <si>
-    <t>LP-052430</t>
-  </si>
-  <si>
-    <t>LP-052465</t>
-  </si>
-  <si>
     <t>LP-052479</t>
-  </si>
-  <si>
-    <t>LP-052511</t>
-  </si>
-  <si>
-    <t>LP-052512</t>
-  </si>
-  <si>
-    <t>LP-052516</t>
-  </si>
-  <si>
-    <t>LP-052518</t>
-  </si>
-  <si>
-    <t>LP-052537</t>
   </si>
 </sst>
 </file>
@@ -664,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1035,220 +915,32 @@
       <c r="A46" t="s">
         <v>49</v>
       </c>
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>50</v>
       </c>
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>92</v>
+      <c r="B49" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB74030A-5DCA-493C-96EC-1EFA5C812C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F050111-1A59-4C19-ABFF-37520F113F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="131">
   <si>
     <t>LP</t>
   </si>
@@ -31,157 +31,391 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-050151</t>
-  </si>
-  <si>
-    <t>Possui linhas de compra e apontamento!</t>
-  </si>
-  <si>
-    <t>LP-050440</t>
-  </si>
-  <si>
-    <t>LP-050554</t>
-  </si>
-  <si>
-    <t>LP-050574</t>
-  </si>
-  <si>
-    <t>LP-050593</t>
-  </si>
-  <si>
-    <t>LP-050621</t>
-  </si>
-  <si>
-    <t>LP-050630</t>
-  </si>
-  <si>
-    <t>LP-051602</t>
+    <t>LP-050184</t>
+  </si>
+  <si>
+    <t>LP-050928</t>
+  </si>
+  <si>
+    <t>LP-051111</t>
+  </si>
+  <si>
+    <t>LP-051504</t>
+  </si>
+  <si>
+    <t>LP-051575</t>
+  </si>
+  <si>
+    <t>LP-051610</t>
+  </si>
+  <si>
+    <t>LP-051617</t>
+  </si>
+  <si>
+    <t>LP-051618</t>
+  </si>
+  <si>
+    <t>LP-051936</t>
+  </si>
+  <si>
+    <t>LP-052034</t>
+  </si>
+  <si>
+    <t>LP-052135</t>
+  </si>
+  <si>
+    <t>LP-052164</t>
+  </si>
+  <si>
+    <t>LP-052209</t>
+  </si>
+  <si>
+    <t>LP-052011</t>
+  </si>
+  <si>
+    <t>LP-052212</t>
+  </si>
+  <si>
+    <t>LP-052230</t>
+  </si>
+  <si>
+    <t>LP-052324</t>
+  </si>
+  <si>
+    <t>LP-052330</t>
+  </si>
+  <si>
+    <t>LP-052358</t>
+  </si>
+  <si>
+    <t>LP-052473</t>
+  </si>
+  <si>
+    <t>LP-052481</t>
+  </si>
+  <si>
+    <t>LP-052482</t>
+  </si>
+  <si>
+    <t>LP-052483</t>
+  </si>
+  <si>
+    <t>LP-052484</t>
+  </si>
+  <si>
+    <t>LP-052485</t>
+  </si>
+  <si>
+    <t>LP-052493</t>
+  </si>
+  <si>
+    <t>LP-052507</t>
+  </si>
+  <si>
+    <t>LP-052520</t>
+  </si>
+  <si>
+    <t>LP-052534</t>
+  </si>
+  <si>
+    <t>LP-052547</t>
+  </si>
+  <si>
+    <t>LP-052559</t>
+  </si>
+  <si>
+    <t>LP-052615</t>
+  </si>
+  <si>
+    <t>LP-052617</t>
+  </si>
+  <si>
+    <t>LP-052618</t>
+  </si>
+  <si>
+    <t>LP-052619</t>
+  </si>
+  <si>
+    <t>LP-052632</t>
+  </si>
+  <si>
+    <t>LP-052639</t>
+  </si>
+  <si>
+    <t>LP-049140</t>
+  </si>
+  <si>
+    <t>LP-050614</t>
+  </si>
+  <si>
+    <t>LP-050717</t>
+  </si>
+  <si>
+    <t>LP-051068</t>
+  </si>
+  <si>
+    <t>LP-051219</t>
+  </si>
+  <si>
+    <t>LP-051305</t>
+  </si>
+  <si>
+    <t>LP-051390</t>
+  </si>
+  <si>
+    <t>LP-051444</t>
+  </si>
+  <si>
+    <t>LP-051445</t>
+  </si>
+  <si>
+    <t>LP-051446</t>
+  </si>
+  <si>
+    <t>LP-051702</t>
+  </si>
+  <si>
+    <t>LP-051713</t>
+  </si>
+  <si>
+    <t>LP-051724</t>
+  </si>
+  <si>
+    <t>LP-051725</t>
+  </si>
+  <si>
+    <t>LP-051776</t>
+  </si>
+  <si>
+    <t>LP-051945</t>
+  </si>
+  <si>
+    <t>LP-052044</t>
+  </si>
+  <si>
+    <t>LP-052062</t>
+  </si>
+  <si>
+    <t>LP-052097</t>
+  </si>
+  <si>
+    <t>LP-052099</t>
+  </si>
+  <si>
+    <t>LP-052137</t>
+  </si>
+  <si>
+    <t>LP-052328</t>
+  </si>
+  <si>
+    <t>LP-052402</t>
+  </si>
+  <si>
+    <t>LP-051606</t>
+  </si>
+  <si>
+    <t>LP-051609</t>
+  </si>
+  <si>
+    <t>LP-051627</t>
+  </si>
+  <si>
+    <t>LP-051656</t>
+  </si>
+  <si>
+    <t>LP-051659</t>
+  </si>
+  <si>
+    <t>LP-051681</t>
+  </si>
+  <si>
+    <t>LP-051686</t>
+  </si>
+  <si>
+    <t>LP-051687</t>
+  </si>
+  <si>
+    <t>LP-051736</t>
+  </si>
+  <si>
+    <t>LP-051753</t>
+  </si>
+  <si>
+    <t>LP-051754</t>
+  </si>
+  <si>
+    <t>LP-051902</t>
+  </si>
+  <si>
+    <t>LP-051922</t>
+  </si>
+  <si>
+    <t>LP-051913</t>
+  </si>
+  <si>
+    <t>LP-051930</t>
+  </si>
+  <si>
+    <t>LP-051966</t>
+  </si>
+  <si>
+    <t>LP-052012</t>
+  </si>
+  <si>
+    <t>LP-052026</t>
+  </si>
+  <si>
+    <t>LP-052076</t>
+  </si>
+  <si>
+    <t>LP-052132</t>
+  </si>
+  <si>
+    <t>LP-052151</t>
+  </si>
+  <si>
+    <t>LP-052196</t>
+  </si>
+  <si>
+    <t>LP-052213</t>
+  </si>
+  <si>
+    <t>LP-052290</t>
+  </si>
+  <si>
+    <t>LP-052363</t>
+  </si>
+  <si>
+    <t>LP-052413</t>
+  </si>
+  <si>
+    <t>LP-052476</t>
+  </si>
+  <si>
+    <t>LP-052500</t>
+  </si>
+  <si>
+    <t>LP-052501</t>
+  </si>
+  <si>
+    <t>LP-052596</t>
+  </si>
+  <si>
+    <t>LP-052621</t>
+  </si>
+  <si>
+    <t>LP-052635</t>
+  </si>
+  <si>
+    <t>LP-052653</t>
+  </si>
+  <si>
+    <t>LP-052664</t>
+  </si>
+  <si>
+    <t>LP-052783</t>
+  </si>
+  <si>
+    <t>LP-052812</t>
+  </si>
+  <si>
+    <t>LP-043883</t>
+  </si>
+  <si>
+    <t>LP-044151</t>
+  </si>
+  <si>
+    <t>LP-045270</t>
+  </si>
+  <si>
+    <t>LP-046595</t>
+  </si>
+  <si>
+    <t>LP-047208</t>
+  </si>
+  <si>
+    <t>LP-047224</t>
+  </si>
+  <si>
+    <t>LP-047618</t>
+  </si>
+  <si>
+    <t>LP-047619</t>
+  </si>
+  <si>
+    <t>LP-048102</t>
+  </si>
+  <si>
+    <t>LP-048697</t>
+  </si>
+  <si>
+    <t>LP-049187</t>
+  </si>
+  <si>
+    <t>LP-049188</t>
+  </si>
+  <si>
+    <t>LP-049189</t>
+  </si>
+  <si>
+    <t>LP-049190</t>
+  </si>
+  <si>
+    <t>LP-049191</t>
+  </si>
+  <si>
+    <t>LP-049716</t>
+  </si>
+  <si>
+    <t>LP-049891</t>
+  </si>
+  <si>
+    <t>LP-050304</t>
   </si>
   <si>
     <t>LP-050367</t>
   </si>
   <si>
-    <t>LP-050486</t>
-  </si>
-  <si>
-    <t>LP-050565</t>
-  </si>
-  <si>
-    <t>LP-050958</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-051570</t>
-  </si>
-  <si>
-    <t>LP-051629</t>
-  </si>
-  <si>
-    <t>LP-051684</t>
-  </si>
-  <si>
-    <t>LP-051845</t>
-  </si>
-  <si>
-    <t>LP-051846</t>
-  </si>
-  <si>
-    <t>LP-051847</t>
-  </si>
-  <si>
-    <t>LP-051859</t>
-  </si>
-  <si>
-    <t>LP-051865</t>
-  </si>
-  <si>
-    <t>LP-051866</t>
-  </si>
-  <si>
-    <t>LP-051931</t>
-  </si>
-  <si>
-    <t>LP-050538</t>
-  </si>
-  <si>
-    <t>LP-050608</t>
-  </si>
-  <si>
-    <t>LP-051375</t>
-  </si>
-  <si>
-    <t>LP-051409</t>
-  </si>
-  <si>
-    <t>LP-051498</t>
-  </si>
-  <si>
-    <t>LP-051501</t>
-  </si>
-  <si>
-    <t>LP-051502</t>
-  </si>
-  <si>
-    <t>LP-051506</t>
-  </si>
-  <si>
-    <t>LP-051507</t>
-  </si>
-  <si>
-    <t>LP-051601</t>
-  </si>
-  <si>
-    <t>LP-051603</t>
-  </si>
-  <si>
-    <t>LP-051604</t>
-  </si>
-  <si>
-    <t>LP-051605</t>
-  </si>
-  <si>
-    <t>LP-051664</t>
-  </si>
-  <si>
-    <t>LP-051665</t>
-  </si>
-  <si>
-    <t>LP-051485</t>
-  </si>
-  <si>
-    <t>LP-048389</t>
-  </si>
-  <si>
-    <t>LP-048982</t>
-  </si>
-  <si>
-    <t>LP-549852</t>
-  </si>
-  <si>
-    <t>LP não existe!</t>
-  </si>
-  <si>
-    <t>LP-050276</t>
-  </si>
-  <si>
-    <t>LP-050719</t>
-  </si>
-  <si>
-    <t>LP-052098</t>
-  </si>
-  <si>
-    <t>LP-051626</t>
-  </si>
-  <si>
-    <t>LP-051658</t>
-  </si>
-  <si>
-    <t>LP-051756</t>
-  </si>
-  <si>
-    <t>LP-052479</t>
+    <t>LP-050455</t>
+  </si>
+  <si>
+    <t>LP-050501</t>
+  </si>
+  <si>
+    <t>LP-050870</t>
+  </si>
+  <si>
+    <t>LP-050974</t>
+  </si>
+  <si>
+    <t>LP-051110</t>
+  </si>
+  <si>
+    <t>LP-051228</t>
+  </si>
+  <si>
+    <t>LP-051269</t>
+  </si>
+  <si>
+    <t>LP-051271</t>
+  </si>
+  <si>
+    <t>LP-051377</t>
+  </si>
+  <si>
+    <t>LP-051384</t>
+  </si>
+  <si>
+    <t>LP-051494</t>
+  </si>
+  <si>
+    <t>LP-051495</t>
+  </si>
+  <si>
+    <t>LP-051591</t>
+  </si>
+  <si>
+    <t>LP-051599</t>
   </si>
 </sst>
 </file>
@@ -544,11 +778,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -563,384 +797,655 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B32" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B35" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B36" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="B37" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B38" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="B39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>42</v>
       </c>
-      <c r="B40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>43</v>
       </c>
-      <c r="B41" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>44</v>
       </c>
-      <c r="B42" t="s">
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>46</v>
       </c>
-      <c r="B43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>47</v>
       </c>
-      <c r="B44" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>48</v>
       </c>
-      <c r="B45" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>49</v>
       </c>
-      <c r="B46" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>50</v>
       </c>
-      <c r="B47" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>51</v>
       </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>52</v>
       </c>
-      <c r="B49" t="s">
-        <v>15</v>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F050111-1A59-4C19-ABFF-37520F113F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A14C009-D1DE-41B9-9B21-FB7469AF31DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$76</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="78">
   <si>
     <t>LP</t>
   </si>
@@ -31,22 +31,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-050184</t>
-  </si>
-  <si>
-    <t>LP-050928</t>
-  </si>
-  <si>
-    <t>LP-051111</t>
-  </si>
-  <si>
-    <t>LP-051504</t>
-  </si>
-  <si>
     <t>LP-051575</t>
   </si>
   <si>
-    <t>LP-051610</t>
+    <t>Possui linhas de compra e apontamento!</t>
   </si>
   <si>
     <t>LP-051617</t>
@@ -55,162 +43,18 @@
     <t>LP-051618</t>
   </si>
   <si>
-    <t>LP-051936</t>
-  </si>
-  <si>
     <t>LP-052034</t>
   </si>
   <si>
     <t>LP-052135</t>
   </si>
   <si>
-    <t>LP-052164</t>
-  </si>
-  <si>
-    <t>LP-052209</t>
-  </si>
-  <si>
     <t>LP-052011</t>
   </si>
   <si>
-    <t>LP-052212</t>
-  </si>
-  <si>
-    <t>LP-052230</t>
-  </si>
-  <si>
-    <t>LP-052324</t>
-  </si>
-  <si>
     <t>LP-052330</t>
   </si>
   <si>
-    <t>LP-052358</t>
-  </si>
-  <si>
-    <t>LP-052473</t>
-  </si>
-  <si>
-    <t>LP-052481</t>
-  </si>
-  <si>
-    <t>LP-052482</t>
-  </si>
-  <si>
-    <t>LP-052483</t>
-  </si>
-  <si>
-    <t>LP-052484</t>
-  </si>
-  <si>
-    <t>LP-052485</t>
-  </si>
-  <si>
-    <t>LP-052493</t>
-  </si>
-  <si>
-    <t>LP-052507</t>
-  </si>
-  <si>
-    <t>LP-052520</t>
-  </si>
-  <si>
-    <t>LP-052534</t>
-  </si>
-  <si>
-    <t>LP-052547</t>
-  </si>
-  <si>
-    <t>LP-052559</t>
-  </si>
-  <si>
-    <t>LP-052615</t>
-  </si>
-  <si>
-    <t>LP-052617</t>
-  </si>
-  <si>
-    <t>LP-052618</t>
-  </si>
-  <si>
-    <t>LP-052619</t>
-  </si>
-  <si>
-    <t>LP-052632</t>
-  </si>
-  <si>
-    <t>LP-052639</t>
-  </si>
-  <si>
-    <t>LP-049140</t>
-  </si>
-  <si>
-    <t>LP-050614</t>
-  </si>
-  <si>
-    <t>LP-050717</t>
-  </si>
-  <si>
-    <t>LP-051068</t>
-  </si>
-  <si>
-    <t>LP-051219</t>
-  </si>
-  <si>
-    <t>LP-051305</t>
-  </si>
-  <si>
-    <t>LP-051390</t>
-  </si>
-  <si>
-    <t>LP-051444</t>
-  </si>
-  <si>
-    <t>LP-051445</t>
-  </si>
-  <si>
-    <t>LP-051446</t>
-  </si>
-  <si>
-    <t>LP-051702</t>
-  </si>
-  <si>
-    <t>LP-051713</t>
-  </si>
-  <si>
-    <t>LP-051724</t>
-  </si>
-  <si>
-    <t>LP-051725</t>
-  </si>
-  <si>
-    <t>LP-051776</t>
-  </si>
-  <si>
-    <t>LP-051945</t>
-  </si>
-  <si>
-    <t>LP-052044</t>
-  </si>
-  <si>
-    <t>LP-052062</t>
-  </si>
-  <si>
-    <t>LP-052097</t>
-  </si>
-  <si>
-    <t>LP-052099</t>
-  </si>
-  <si>
-    <t>LP-052137</t>
-  </si>
-  <si>
-    <t>LP-052328</t>
-  </si>
-  <si>
-    <t>LP-052402</t>
-  </si>
-  <si>
     <t>LP-051606</t>
   </si>
   <si>
@@ -224,9 +68,6 @@
   </si>
   <si>
     <t>LP-051659</t>
-  </si>
-  <si>
-    <t>LP-051681</t>
   </si>
   <si>
     <t>LP-051686</t>
@@ -778,11 +619,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -797,655 +638,405 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A14C009-D1DE-41B9-9B21-FB7469AF31DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4948F1F-9347-476A-906D-D69169E8C56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$32</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
   <si>
     <t>LP</t>
   </si>
@@ -43,18 +43,12 @@
     <t>LP-051618</t>
   </si>
   <si>
-    <t>LP-052034</t>
-  </si>
-  <si>
     <t>LP-052135</t>
   </si>
   <si>
     <t>LP-052011</t>
   </si>
   <si>
-    <t>LP-052330</t>
-  </si>
-  <si>
     <t>LP-051606</t>
   </si>
   <si>
@@ -88,126 +82,30 @@
     <t>LP-051902</t>
   </si>
   <si>
-    <t>LP-051922</t>
-  </si>
-  <si>
-    <t>LP-051913</t>
-  </si>
-  <si>
     <t>LP-051930</t>
   </si>
   <si>
     <t>LP-051966</t>
   </si>
   <si>
-    <t>LP-052012</t>
-  </si>
-  <si>
-    <t>LP-052026</t>
-  </si>
-  <si>
     <t>LP-052076</t>
   </si>
   <si>
-    <t>LP-052132</t>
-  </si>
-  <si>
-    <t>LP-052151</t>
-  </si>
-  <si>
-    <t>LP-052196</t>
-  </si>
-  <si>
     <t>LP-052213</t>
   </si>
   <si>
-    <t>LP-052290</t>
+    <t>Compromisso pendente!</t>
   </si>
   <si>
     <t>LP-052363</t>
   </si>
   <si>
-    <t>LP-052413</t>
-  </si>
-  <si>
-    <t>LP-052476</t>
-  </si>
-  <si>
     <t>LP-052500</t>
   </si>
   <si>
-    <t>LP-052501</t>
-  </si>
-  <si>
-    <t>LP-052596</t>
-  </si>
-  <si>
-    <t>LP-052621</t>
-  </si>
-  <si>
-    <t>LP-052635</t>
-  </si>
-  <si>
-    <t>LP-052653</t>
-  </si>
-  <si>
-    <t>LP-052664</t>
-  </si>
-  <si>
-    <t>LP-052783</t>
-  </si>
-  <si>
-    <t>LP-052812</t>
-  </si>
-  <si>
-    <t>LP-043883</t>
-  </si>
-  <si>
     <t>LP-044151</t>
   </si>
   <si>
-    <t>LP-045270</t>
-  </si>
-  <si>
-    <t>LP-046595</t>
-  </si>
-  <si>
-    <t>LP-047208</t>
-  </si>
-  <si>
-    <t>LP-047224</t>
-  </si>
-  <si>
-    <t>LP-047618</t>
-  </si>
-  <si>
-    <t>LP-047619</t>
-  </si>
-  <si>
-    <t>LP-048102</t>
-  </si>
-  <si>
-    <t>LP-048697</t>
-  </si>
-  <si>
-    <t>LP-049187</t>
-  </si>
-  <si>
-    <t>LP-049188</t>
-  </si>
-  <si>
-    <t>LP-049189</t>
-  </si>
-  <si>
-    <t>LP-049190</t>
-  </si>
-  <si>
-    <t>LP-049191</t>
-  </si>
-  <si>
-    <t>LP-049716</t>
-  </si>
-  <si>
     <t>LP-049891</t>
   </si>
   <si>
@@ -217,43 +115,16 @@
     <t>LP-050367</t>
   </si>
   <si>
-    <t>LP-050455</t>
-  </si>
-  <si>
     <t>LP-050501</t>
   </si>
   <si>
-    <t>LP-050870</t>
-  </si>
-  <si>
-    <t>LP-050974</t>
-  </si>
-  <si>
-    <t>LP-051110</t>
-  </si>
-  <si>
     <t>LP-051228</t>
   </si>
   <si>
-    <t>LP-051269</t>
-  </si>
-  <si>
-    <t>LP-051271</t>
-  </si>
-  <si>
-    <t>LP-051377</t>
-  </si>
-  <si>
-    <t>LP-051384</t>
-  </si>
-  <si>
     <t>LP-051494</t>
   </si>
   <si>
     <t>LP-051495</t>
-  </si>
-  <si>
-    <t>LP-051591</t>
   </si>
   <si>
     <t>LP-051599</t>
@@ -619,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -660,7 +531,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -668,7 +539,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -676,7 +547,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -684,7 +555,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -692,7 +563,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -700,7 +571,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -708,7 +579,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -716,327 +587,170 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>77</v>
+      <c r="B32" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4948F1F-9347-476A-906D-D69169E8C56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3F8A57-D7DC-42B2-92B1-BC393CF70423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="96">
   <si>
     <t>LP</t>
   </si>
@@ -31,103 +31,286 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-051575</t>
-  </si>
-  <si>
-    <t>Possui linhas de compra e apontamento!</t>
-  </si>
-  <si>
-    <t>LP-051617</t>
-  </si>
-  <si>
-    <t>LP-051618</t>
-  </si>
-  <si>
-    <t>LP-052135</t>
-  </si>
-  <si>
-    <t>LP-052011</t>
-  </si>
-  <si>
-    <t>LP-051606</t>
-  </si>
-  <si>
-    <t>LP-051609</t>
-  </si>
-  <si>
-    <t>LP-051627</t>
-  </si>
-  <si>
-    <t>LP-051656</t>
-  </si>
-  <si>
-    <t>LP-051659</t>
-  </si>
-  <si>
-    <t>LP-051686</t>
-  </si>
-  <si>
-    <t>LP-051687</t>
-  </si>
-  <si>
-    <t>LP-051736</t>
-  </si>
-  <si>
-    <t>LP-051753</t>
-  </si>
-  <si>
-    <t>LP-051754</t>
-  </si>
-  <si>
-    <t>LP-051902</t>
-  </si>
-  <si>
-    <t>LP-051930</t>
-  </si>
-  <si>
-    <t>LP-051966</t>
-  </si>
-  <si>
-    <t>LP-052076</t>
-  </si>
-  <si>
-    <t>LP-052213</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-052363</t>
-  </si>
-  <si>
-    <t>LP-052500</t>
-  </si>
-  <si>
-    <t>LP-044151</t>
-  </si>
-  <si>
-    <t>LP-049891</t>
-  </si>
-  <si>
-    <t>LP-050304</t>
-  </si>
-  <si>
-    <t>LP-050367</t>
-  </si>
-  <si>
-    <t>LP-050501</t>
-  </si>
-  <si>
-    <t>LP-051228</t>
-  </si>
-  <si>
-    <t>LP-051494</t>
-  </si>
-  <si>
-    <t>LP-051495</t>
-  </si>
-  <si>
-    <t>LP-051599</t>
+    <t>LP-039759</t>
+  </si>
+  <si>
+    <t>LP-040769</t>
+  </si>
+  <si>
+    <t>LP-047128</t>
+  </si>
+  <si>
+    <t>LP-047983</t>
+  </si>
+  <si>
+    <t>LP-049262</t>
+  </si>
+  <si>
+    <t>LP-049405</t>
+  </si>
+  <si>
+    <t>LP-049643</t>
+  </si>
+  <si>
+    <t>LP-049688</t>
+  </si>
+  <si>
+    <t>LP-050001</t>
+  </si>
+  <si>
+    <t>LP-050381</t>
+  </si>
+  <si>
+    <t>LP-050617</t>
+  </si>
+  <si>
+    <t>LP-051070</t>
+  </si>
+  <si>
+    <t>LP-051164</t>
+  </si>
+  <si>
+    <t>LP-051191</t>
+  </si>
+  <si>
+    <t>LP-051216</t>
+  </si>
+  <si>
+    <t>LP-051223</t>
+  </si>
+  <si>
+    <t>LP-051233</t>
+  </si>
+  <si>
+    <t>LP-051226</t>
+  </si>
+  <si>
+    <t>LP-051263</t>
+  </si>
+  <si>
+    <t>LP-051320</t>
+  </si>
+  <si>
+    <t>LP-051497</t>
+  </si>
+  <si>
+    <t>LP-051624</t>
+  </si>
+  <si>
+    <t>LP-051680</t>
+  </si>
+  <si>
+    <t>LP-051682</t>
+  </si>
+  <si>
+    <t>LP-051683</t>
+  </si>
+  <si>
+    <t>LP-051685</t>
+  </si>
+  <si>
+    <t>LP-051709</t>
+  </si>
+  <si>
+    <t>LP-051745</t>
+  </si>
+  <si>
+    <t>LP-051746</t>
+  </si>
+  <si>
+    <t>LP-051749</t>
+  </si>
+  <si>
+    <t>LP-051750</t>
+  </si>
+  <si>
+    <t>LP-051883</t>
+  </si>
+  <si>
+    <t>LP-051884</t>
+  </si>
+  <si>
+    <t>LP-051887</t>
+  </si>
+  <si>
+    <t>LP-051903</t>
+  </si>
+  <si>
+    <t>LP-051904</t>
+  </si>
+  <si>
+    <t>LP-051905</t>
+  </si>
+  <si>
+    <t>LP-051906</t>
+  </si>
+  <si>
+    <t>LP-051907</t>
+  </si>
+  <si>
+    <t>LP-051908</t>
+  </si>
+  <si>
+    <t>LP-051909</t>
+  </si>
+  <si>
+    <t>LP-051910</t>
+  </si>
+  <si>
+    <t>LP-052008</t>
+  </si>
+  <si>
+    <t>LP-052009</t>
+  </si>
+  <si>
+    <t>LP-052017</t>
+  </si>
+  <si>
+    <t>LP-052018</t>
+  </si>
+  <si>
+    <t>LP-052028</t>
+  </si>
+  <si>
+    <t>LP-052029</t>
+  </si>
+  <si>
+    <t>LP-052030</t>
+  </si>
+  <si>
+    <t>LP-052031</t>
+  </si>
+  <si>
+    <t>LP-052032</t>
+  </si>
+  <si>
+    <t>LP-052061</t>
+  </si>
+  <si>
+    <t>LP-052093</t>
+  </si>
+  <si>
+    <t>LP-052108</t>
+  </si>
+  <si>
+    <t>LP-052109</t>
+  </si>
+  <si>
+    <t>LP-052136</t>
+  </si>
+  <si>
+    <t>LP-052148</t>
+  </si>
+  <si>
+    <t>LP-052153</t>
+  </si>
+  <si>
+    <t>LP-052152</t>
+  </si>
+  <si>
+    <t>LP-052212</t>
+  </si>
+  <si>
+    <t>LP-052214</t>
+  </si>
+  <si>
+    <t>LP-052262</t>
+  </si>
+  <si>
+    <t>LP-052480</t>
+  </si>
+  <si>
+    <t>LP-052487</t>
+  </si>
+  <si>
+    <t>LP-052504</t>
+  </si>
+  <si>
+    <t>LP-052508</t>
+  </si>
+  <si>
+    <t>LP-052509</t>
+  </si>
+  <si>
+    <t>LP-052513</t>
+  </si>
+  <si>
+    <t>LP-052514</t>
+  </si>
+  <si>
+    <t>LP-052572</t>
+  </si>
+  <si>
+    <t>LP-052608</t>
+  </si>
+  <si>
+    <t>LP-052628</t>
+  </si>
+  <si>
+    <t>LP-052688</t>
+  </si>
+  <si>
+    <t>LP-052782</t>
+  </si>
+  <si>
+    <t>LP-052861</t>
+  </si>
+  <si>
+    <t>LP-052986</t>
+  </si>
+  <si>
+    <t>LP-045478</t>
+  </si>
+  <si>
+    <t>LP-045674</t>
+  </si>
+  <si>
+    <t>LP-048423</t>
+  </si>
+  <si>
+    <t>LP-048713</t>
+  </si>
+  <si>
+    <t>LP-048714</t>
+  </si>
+  <si>
+    <t>LP-049936</t>
+  </si>
+  <si>
+    <t>LP-050094</t>
+  </si>
+  <si>
+    <t>LP-050096</t>
+  </si>
+  <si>
+    <t>LP-050127</t>
+  </si>
+  <si>
+    <t>LP-050143</t>
+  </si>
+  <si>
+    <t>LP-050419</t>
+  </si>
+  <si>
+    <t>LP-051029</t>
+  </si>
+  <si>
+    <t>LP-051030</t>
+  </si>
+  <si>
+    <t>LP-051221</t>
+  </si>
+  <si>
+    <t>LP-051517</t>
+  </si>
+  <si>
+    <t>LP-051544</t>
+  </si>
+  <si>
+    <t>LP-051701</t>
+  </si>
+  <si>
+    <t>LP-052163</t>
   </si>
 </sst>
 </file>
@@ -490,11 +673,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -509,248 +692,480 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B29" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B32" t="s">
-        <v>3</v>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3F8A57-D7DC-42B2-92B1-BC393CF70423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7C55ED-4680-4AB8-8F0C-53E597EE62F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$80</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
   <si>
     <t>LP</t>
   </si>
@@ -31,58 +31,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-039759</t>
-  </si>
-  <si>
-    <t>LP-040769</t>
-  </si>
-  <si>
-    <t>LP-047128</t>
-  </si>
-  <si>
-    <t>LP-047983</t>
-  </si>
-  <si>
-    <t>LP-049262</t>
-  </si>
-  <si>
-    <t>LP-049405</t>
-  </si>
-  <si>
-    <t>LP-049643</t>
-  </si>
-  <si>
-    <t>LP-049688</t>
-  </si>
-  <si>
     <t>LP-050001</t>
   </si>
   <si>
-    <t>LP-050381</t>
-  </si>
-  <si>
-    <t>LP-050617</t>
-  </si>
-  <si>
-    <t>LP-051070</t>
-  </si>
-  <si>
-    <t>LP-051164</t>
-  </si>
-  <si>
-    <t>LP-051191</t>
-  </si>
-  <si>
-    <t>LP-051216</t>
-  </si>
-  <si>
-    <t>LP-051223</t>
-  </si>
-  <si>
-    <t>LP-051233</t>
-  </si>
-  <si>
-    <t>LP-051226</t>
+    <t>Possui linhas de compra e apontamento!</t>
   </si>
   <si>
     <t>LP-051263</t>
@@ -673,11 +625,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -692,85 +644,88 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -855,132 +810,132 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
@@ -1070,102 +1025,17 @@
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7C55ED-4680-4AB8-8F0C-53E597EE62F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD0DCE1-A742-4978-BC15-3BD15206B2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$40</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="41">
   <si>
     <t>LP</t>
   </si>
@@ -37,18 +37,9 @@
     <t>Possui linhas de compra e apontamento!</t>
   </si>
   <si>
-    <t>LP-051263</t>
-  </si>
-  <si>
-    <t>LP-051320</t>
-  </si>
-  <si>
     <t>LP-051497</t>
   </si>
   <si>
-    <t>LP-051624</t>
-  </si>
-  <si>
     <t>LP-051680</t>
   </si>
   <si>
@@ -121,121 +112,13 @@
     <t>LP-052018</t>
   </si>
   <si>
-    <t>LP-052028</t>
-  </si>
-  <si>
-    <t>LP-052029</t>
-  </si>
-  <si>
-    <t>LP-052030</t>
-  </si>
-  <si>
-    <t>LP-052031</t>
-  </si>
-  <si>
-    <t>LP-052032</t>
-  </si>
-  <si>
-    <t>LP-052061</t>
-  </si>
-  <si>
-    <t>LP-052093</t>
-  </si>
-  <si>
-    <t>LP-052108</t>
-  </si>
-  <si>
-    <t>LP-052109</t>
-  </si>
-  <si>
-    <t>LP-052136</t>
-  </si>
-  <si>
-    <t>LP-052148</t>
-  </si>
-  <si>
     <t>LP-052153</t>
   </si>
   <si>
-    <t>LP-052152</t>
-  </si>
-  <si>
-    <t>LP-052212</t>
-  </si>
-  <si>
-    <t>LP-052214</t>
-  </si>
-  <si>
-    <t>LP-052262</t>
-  </si>
-  <si>
-    <t>LP-052480</t>
-  </si>
-  <si>
-    <t>LP-052487</t>
-  </si>
-  <si>
-    <t>LP-052504</t>
-  </si>
-  <si>
-    <t>LP-052508</t>
-  </si>
-  <si>
-    <t>LP-052509</t>
-  </si>
-  <si>
-    <t>LP-052513</t>
-  </si>
-  <si>
-    <t>LP-052514</t>
-  </si>
-  <si>
-    <t>LP-052572</t>
-  </si>
-  <si>
-    <t>LP-052608</t>
-  </si>
-  <si>
-    <t>LP-052628</t>
-  </si>
-  <si>
-    <t>LP-052688</t>
-  </si>
-  <si>
-    <t>LP-052782</t>
-  </si>
-  <si>
-    <t>LP-052861</t>
-  </si>
-  <si>
-    <t>LP-052986</t>
-  </si>
-  <si>
-    <t>LP-045478</t>
-  </si>
-  <si>
-    <t>LP-045674</t>
-  </si>
-  <si>
-    <t>LP-048423</t>
-  </si>
-  <si>
     <t>LP-048713</t>
   </si>
   <si>
     <t>LP-048714</t>
-  </si>
-  <si>
-    <t>LP-049936</t>
-  </si>
-  <si>
-    <t>LP-050094</t>
-  </si>
-  <si>
-    <t>LP-050096</t>
-  </si>
-  <si>
-    <t>LP-050127</t>
   </si>
   <si>
     <t>LP-050143</t>
@@ -625,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -652,148 +535,235 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -836,206 +806,6 @@
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD0DCE1-A742-4978-BC15-3BD15206B2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EF6994-470C-4D2B-9C25-7F6878C8DF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t>LP</t>
   </si>
@@ -31,121 +31,436 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-050001</t>
-  </si>
-  <si>
-    <t>Possui linhas de compra e apontamento!</t>
-  </si>
-  <si>
-    <t>LP-051497</t>
-  </si>
-  <si>
-    <t>LP-051680</t>
-  </si>
-  <si>
-    <t>LP-051682</t>
-  </si>
-  <si>
-    <t>LP-051683</t>
-  </si>
-  <si>
-    <t>LP-051685</t>
-  </si>
-  <si>
-    <t>LP-051709</t>
-  </si>
-  <si>
-    <t>LP-051745</t>
-  </si>
-  <si>
-    <t>LP-051746</t>
-  </si>
-  <si>
-    <t>LP-051749</t>
-  </si>
-  <si>
-    <t>LP-051750</t>
-  </si>
-  <si>
-    <t>LP-051883</t>
-  </si>
-  <si>
-    <t>LP-051884</t>
-  </si>
-  <si>
-    <t>LP-051887</t>
-  </si>
-  <si>
-    <t>LP-051903</t>
-  </si>
-  <si>
-    <t>LP-051904</t>
-  </si>
-  <si>
-    <t>LP-051905</t>
-  </si>
-  <si>
-    <t>LP-051906</t>
-  </si>
-  <si>
-    <t>LP-051907</t>
-  </si>
-  <si>
-    <t>LP-051908</t>
-  </si>
-  <si>
-    <t>LP-051909</t>
-  </si>
-  <si>
-    <t>LP-051910</t>
-  </si>
-  <si>
-    <t>LP-052008</t>
-  </si>
-  <si>
-    <t>LP-052009</t>
-  </si>
-  <si>
-    <t>LP-052017</t>
-  </si>
-  <si>
-    <t>LP-052018</t>
-  </si>
-  <si>
-    <t>LP-052153</t>
-  </si>
-  <si>
-    <t>LP-048713</t>
-  </si>
-  <si>
-    <t>LP-048714</t>
-  </si>
-  <si>
-    <t>LP-050143</t>
-  </si>
-  <si>
-    <t>LP-050419</t>
-  </si>
-  <si>
-    <t>LP-051029</t>
-  </si>
-  <si>
-    <t>LP-051030</t>
-  </si>
-  <si>
-    <t>LP-051221</t>
-  </si>
-  <si>
-    <t>LP-051517</t>
-  </si>
-  <si>
-    <t>LP-051544</t>
-  </si>
-  <si>
-    <t>LP-051701</t>
-  </si>
-  <si>
-    <t>LP-052163</t>
+    <t>LP-007876</t>
+  </si>
+  <si>
+    <t>LP-008079</t>
+  </si>
+  <si>
+    <t>LP-008046</t>
+  </si>
+  <si>
+    <t>LP-008767</t>
+  </si>
+  <si>
+    <t>LP-008769</t>
+  </si>
+  <si>
+    <t>LP-010221</t>
+  </si>
+  <si>
+    <t>LP-011252</t>
+  </si>
+  <si>
+    <t>LP-010943</t>
+  </si>
+  <si>
+    <t>LP-010944</t>
+  </si>
+  <si>
+    <t>LP-011239</t>
+  </si>
+  <si>
+    <t>LP-011914</t>
+  </si>
+  <si>
+    <t>LP-011915</t>
+  </si>
+  <si>
+    <t>LP-011916</t>
+  </si>
+  <si>
+    <t>LP-011917</t>
+  </si>
+  <si>
+    <t>LP-011691</t>
+  </si>
+  <si>
+    <t>LP-011958</t>
+  </si>
+  <si>
+    <t>LP-011949</t>
+  </si>
+  <si>
+    <t>LP-012703</t>
+  </si>
+  <si>
+    <t>LP-012547</t>
+  </si>
+  <si>
+    <t>LP-012702</t>
+  </si>
+  <si>
+    <t>LP-012548</t>
+  </si>
+  <si>
+    <t>LP-013161</t>
+  </si>
+  <si>
+    <t>LP-013337</t>
+  </si>
+  <si>
+    <t>LP-013444</t>
+  </si>
+  <si>
+    <t>LP-014697</t>
+  </si>
+  <si>
+    <t>LP-016075</t>
+  </si>
+  <si>
+    <t>LP-016199</t>
+  </si>
+  <si>
+    <t>LP-017180</t>
+  </si>
+  <si>
+    <t>LP-017093</t>
+  </si>
+  <si>
+    <t>LP-017034</t>
+  </si>
+  <si>
+    <t>LP-017035</t>
+  </si>
+  <si>
+    <t>LP-018651</t>
+  </si>
+  <si>
+    <t>LP-019026</t>
+  </si>
+  <si>
+    <t>LP-018908</t>
+  </si>
+  <si>
+    <t>LP-019151</t>
+  </si>
+  <si>
+    <t>LP-019500</t>
+  </si>
+  <si>
+    <t>LP-019480</t>
+  </si>
+  <si>
+    <t>LP-019552</t>
+  </si>
+  <si>
+    <t>LP-020403</t>
+  </si>
+  <si>
+    <t>LP-020609</t>
+  </si>
+  <si>
+    <t>LP-022028</t>
+  </si>
+  <si>
+    <t>LP-030877</t>
+  </si>
+  <si>
+    <t>LP-031038</t>
+  </si>
+  <si>
+    <t>LP-026526</t>
+  </si>
+  <si>
+    <t>LP-026366</t>
+  </si>
+  <si>
+    <t>LP-026553</t>
+  </si>
+  <si>
+    <t>LP-027839</t>
+  </si>
+  <si>
+    <t>LP-027036</t>
+  </si>
+  <si>
+    <t>LP-027840</t>
+  </si>
+  <si>
+    <t>LP-027818</t>
+  </si>
+  <si>
+    <t>LP-027830</t>
+  </si>
+  <si>
+    <t>LP-028616</t>
+  </si>
+  <si>
+    <t>LP-028618</t>
+  </si>
+  <si>
+    <t>LP-028615</t>
+  </si>
+  <si>
+    <t>LP-028617</t>
+  </si>
+  <si>
+    <t>LP-029253</t>
+  </si>
+  <si>
+    <t>LP-029890</t>
+  </si>
+  <si>
+    <t>LP-029920</t>
+  </si>
+  <si>
+    <t>LP-030878</t>
+  </si>
+  <si>
+    <t>LP-030448</t>
+  </si>
+  <si>
+    <t>LP-031089</t>
+  </si>
+  <si>
+    <t>LP-030860</t>
+  </si>
+  <si>
+    <t>LP-030801</t>
+  </si>
+  <si>
+    <t>LP-031399</t>
+  </si>
+  <si>
+    <t>LP-031498</t>
+  </si>
+  <si>
+    <t>LP-032265</t>
+  </si>
+  <si>
+    <t>LP-032339</t>
+  </si>
+  <si>
+    <t>LP-032473</t>
+  </si>
+  <si>
+    <t>LP-033819</t>
+  </si>
+  <si>
+    <t>LP-033921</t>
+  </si>
+  <si>
+    <t>LP-033202</t>
+  </si>
+  <si>
+    <t>LP-033817</t>
+  </si>
+  <si>
+    <t>LP-033926</t>
+  </si>
+  <si>
+    <t>LP-034178</t>
+  </si>
+  <si>
+    <t>LP-033959</t>
+  </si>
+  <si>
+    <t>LP-033960</t>
+  </si>
+  <si>
+    <t>LP-035078</t>
+  </si>
+  <si>
+    <t>LP-035156</t>
+  </si>
+  <si>
+    <t>LP-035157</t>
+  </si>
+  <si>
+    <t>LP-037846</t>
+  </si>
+  <si>
+    <t>LP-035933</t>
+  </si>
+  <si>
+    <t>LP-037048</t>
+  </si>
+  <si>
+    <t>LP-036886</t>
+  </si>
+  <si>
+    <t>LP-036365</t>
+  </si>
+  <si>
+    <t>LP-036640</t>
+  </si>
+  <si>
+    <t>LP-036951</t>
+  </si>
+  <si>
+    <t>LP-036930</t>
+  </si>
+  <si>
+    <t>LP-036949</t>
+  </si>
+  <si>
+    <t>LP-036950</t>
+  </si>
+  <si>
+    <t>LP-037132</t>
+  </si>
+  <si>
+    <t>LP-037215</t>
+  </si>
+  <si>
+    <t>LP-037996</t>
+  </si>
+  <si>
+    <t>LP-037787</t>
+  </si>
+  <si>
+    <t>LP-038234</t>
+  </si>
+  <si>
+    <t>LP-038213</t>
+  </si>
+  <si>
+    <t>LP-038776</t>
+  </si>
+  <si>
+    <t>LP-041469</t>
+  </si>
+  <si>
+    <t>LP-039481</t>
+  </si>
+  <si>
+    <t>LP-038876</t>
+  </si>
+  <si>
+    <t>LP-038922</t>
+  </si>
+  <si>
+    <t>LP-039045</t>
+  </si>
+  <si>
+    <t>LP-039255</t>
+  </si>
+  <si>
+    <t>LP-039715</t>
+  </si>
+  <si>
+    <t>LP-044496</t>
+  </si>
+  <si>
+    <t>LP-039703</t>
+  </si>
+  <si>
+    <t>LP-039704</t>
+  </si>
+  <si>
+    <t>LP-039705</t>
+  </si>
+  <si>
+    <t>LP-039706</t>
+  </si>
+  <si>
+    <t>LP-039707</t>
+  </si>
+  <si>
+    <t>LP-039708</t>
+  </si>
+  <si>
+    <t>LP-039932</t>
+  </si>
+  <si>
+    <t>LP-039933</t>
+  </si>
+  <si>
+    <t>LP-039934</t>
+  </si>
+  <si>
+    <t>LP-040074</t>
+  </si>
+  <si>
+    <t>LP-041328</t>
+  </si>
+  <si>
+    <t>LP-041420</t>
+  </si>
+  <si>
+    <t>LP-042041</t>
+  </si>
+  <si>
+    <t>LP-041706</t>
+  </si>
+  <si>
+    <t>LP-043746</t>
+  </si>
+  <si>
+    <t>LP-042192</t>
+  </si>
+  <si>
+    <t>LP-043738</t>
+  </si>
+  <si>
+    <t>LP-043086</t>
+  </si>
+  <si>
+    <t>LP-043200</t>
+  </si>
+  <si>
+    <t>LP-043741</t>
+  </si>
+  <si>
+    <t>LP-043942</t>
+  </si>
+  <si>
+    <t>LP-043897</t>
+  </si>
+  <si>
+    <t>LP-044035</t>
+  </si>
+  <si>
+    <t>LP-044279</t>
+  </si>
+  <si>
+    <t>LP-044277</t>
+  </si>
+  <si>
+    <t>LP-044283</t>
+  </si>
+  <si>
+    <t>LP-044284</t>
+  </si>
+  <si>
+    <t>LP-046129</t>
+  </si>
+  <si>
+    <t>LP-046130</t>
+  </si>
+  <si>
+    <t>LP-046078</t>
+  </si>
+  <si>
+    <t>LP-047366</t>
+  </si>
+  <si>
+    <t>LP-047367</t>
+  </si>
+  <si>
+    <t>LP-046128</t>
+  </si>
+  <si>
+    <t>LP-046153</t>
+  </si>
+  <si>
+    <t>LP-046884</t>
+  </si>
+  <si>
+    <t>LP-047311</t>
+  </si>
+  <si>
+    <t>LP-047807</t>
+  </si>
+  <si>
+    <t>LP-047806</t>
+  </si>
+  <si>
+    <t>LP-048060</t>
+  </si>
+  <si>
+    <t>LP-048066</t>
   </si>
 </sst>
 </file>
@@ -164,6 +479,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -508,11 +824,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -527,243 +843,153 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B31" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -806,6 +1032,531 @@
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EF6994-470C-4D2B-9C25-7F6878C8DF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2E09CB-A927-44A1-987F-159CB72691AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$40</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
   <si>
     <t>LP</t>
   </si>
@@ -31,60 +28,12 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-007876</t>
-  </si>
-  <si>
-    <t>LP-008079</t>
-  </si>
-  <si>
-    <t>LP-008046</t>
-  </si>
-  <si>
-    <t>LP-008767</t>
-  </si>
-  <si>
-    <t>LP-008769</t>
-  </si>
-  <si>
-    <t>LP-010221</t>
-  </si>
-  <si>
-    <t>LP-011252</t>
-  </si>
-  <si>
-    <t>LP-010943</t>
-  </si>
-  <si>
-    <t>LP-010944</t>
-  </si>
-  <si>
-    <t>LP-011239</t>
-  </si>
-  <si>
-    <t>LP-011914</t>
-  </si>
-  <si>
-    <t>LP-011915</t>
-  </si>
-  <si>
-    <t>LP-011916</t>
-  </si>
-  <si>
-    <t>LP-011917</t>
-  </si>
-  <si>
-    <t>LP-011691</t>
-  </si>
-  <si>
-    <t>LP-011958</t>
-  </si>
-  <si>
-    <t>LP-011949</t>
-  </si>
-  <si>
     <t>LP-012703</t>
   </si>
   <si>
+    <t>Compromisso pendente!</t>
+  </si>
+  <si>
     <t>LP-012547</t>
   </si>
   <si>
@@ -94,184 +43,10 @@
     <t>LP-012548</t>
   </si>
   <si>
-    <t>LP-013161</t>
-  </si>
-  <si>
-    <t>LP-013337</t>
-  </si>
-  <si>
-    <t>LP-013444</t>
-  </si>
-  <si>
-    <t>LP-014697</t>
-  </si>
-  <si>
-    <t>LP-016075</t>
-  </si>
-  <si>
-    <t>LP-016199</t>
-  </si>
-  <si>
-    <t>LP-017180</t>
-  </si>
-  <si>
-    <t>LP-017093</t>
-  </si>
-  <si>
-    <t>LP-017034</t>
-  </si>
-  <si>
-    <t>LP-017035</t>
-  </si>
-  <si>
-    <t>LP-018651</t>
-  </si>
-  <si>
-    <t>LP-019026</t>
-  </si>
-  <si>
-    <t>LP-018908</t>
-  </si>
-  <si>
-    <t>LP-019151</t>
-  </si>
-  <si>
-    <t>LP-019500</t>
-  </si>
-  <si>
-    <t>LP-019480</t>
-  </si>
-  <si>
-    <t>LP-019552</t>
-  </si>
-  <si>
-    <t>LP-020403</t>
-  </si>
-  <si>
-    <t>LP-020609</t>
-  </si>
-  <si>
-    <t>LP-022028</t>
-  </si>
-  <si>
-    <t>LP-030877</t>
-  </si>
-  <si>
-    <t>LP-031038</t>
-  </si>
-  <si>
-    <t>LP-026526</t>
-  </si>
-  <si>
-    <t>LP-026366</t>
-  </si>
-  <si>
-    <t>LP-026553</t>
-  </si>
-  <si>
-    <t>LP-027839</t>
-  </si>
-  <si>
-    <t>LP-027036</t>
-  </si>
-  <si>
-    <t>LP-027840</t>
-  </si>
-  <si>
-    <t>LP-027818</t>
-  </si>
-  <si>
-    <t>LP-027830</t>
-  </si>
-  <si>
-    <t>LP-028616</t>
-  </si>
-  <si>
-    <t>LP-028618</t>
-  </si>
-  <si>
-    <t>LP-028615</t>
-  </si>
-  <si>
-    <t>LP-028617</t>
-  </si>
-  <si>
-    <t>LP-029253</t>
-  </si>
-  <si>
-    <t>LP-029890</t>
-  </si>
-  <si>
-    <t>LP-029920</t>
-  </si>
-  <si>
-    <t>LP-030878</t>
-  </si>
-  <si>
-    <t>LP-030448</t>
-  </si>
-  <si>
-    <t>LP-031089</t>
-  </si>
-  <si>
-    <t>LP-030860</t>
-  </si>
-  <si>
-    <t>LP-030801</t>
-  </si>
-  <si>
-    <t>LP-031399</t>
-  </si>
-  <si>
-    <t>LP-031498</t>
-  </si>
-  <si>
-    <t>LP-032265</t>
-  </si>
-  <si>
-    <t>LP-032339</t>
-  </si>
-  <si>
-    <t>LP-032473</t>
-  </si>
-  <si>
-    <t>LP-033819</t>
-  </si>
-  <si>
     <t>LP-033921</t>
   </si>
   <si>
-    <t>LP-033202</t>
-  </si>
-  <si>
-    <t>LP-033817</t>
-  </si>
-  <si>
-    <t>LP-033926</t>
-  </si>
-  <si>
     <t>LP-034178</t>
-  </si>
-  <si>
-    <t>LP-033959</t>
-  </si>
-  <si>
-    <t>LP-033960</t>
-  </si>
-  <si>
-    <t>LP-035078</t>
-  </si>
-  <si>
-    <t>LP-035156</t>
-  </si>
-  <si>
-    <t>LP-035157</t>
-  </si>
-  <si>
-    <t>LP-037846</t>
-  </si>
-  <si>
-    <t>LP-035933</t>
   </si>
   <si>
     <t>LP-037048</t>
@@ -479,7 +254,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -824,11 +598,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B145"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -843,720 +617,363 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19557D1-E2EB-4D1D-AFDF-B1F69CA94F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE29602-6ED9-4DF9-90AB-BC397FD3AFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
   <si>
     <t>LP</t>
   </si>
@@ -28,34 +28,289 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-012703</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-012547</t>
-  </si>
-  <si>
-    <t>LP-012702</t>
-  </si>
-  <si>
-    <t>LP-012548</t>
-  </si>
-  <si>
-    <t>LP-033921</t>
-  </si>
-  <si>
-    <t>LP-034178</t>
-  </si>
-  <si>
-    <t>LP-036950</t>
+    <t>LP-050151</t>
+  </si>
+  <si>
+    <t>LP-050440</t>
+  </si>
+  <si>
+    <t>LP-050554</t>
+  </si>
+  <si>
+    <t>LP-050574</t>
+  </si>
+  <si>
+    <t>LP-050593</t>
+  </si>
+  <si>
+    <t>LP-050621</t>
+  </si>
+  <si>
+    <t>LP-050630</t>
+  </si>
+  <si>
+    <t>LP-051602</t>
+  </si>
+  <si>
+    <t>LP-050367</t>
+  </si>
+  <si>
+    <t>LP-050486</t>
+  </si>
+  <si>
+    <t>LP-050565</t>
+  </si>
+  <si>
+    <t>LP-051570</t>
+  </si>
+  <si>
+    <t>LP-051629</t>
+  </si>
+  <si>
+    <t>LP-051684</t>
+  </si>
+  <si>
+    <t>LP-051845</t>
+  </si>
+  <si>
+    <t>LP-051846</t>
+  </si>
+  <si>
+    <t>LP-051847</t>
+  </si>
+  <si>
+    <t>LP-051859</t>
+  </si>
+  <si>
+    <t>LP-051865</t>
+  </si>
+  <si>
+    <t>LP-051866</t>
+  </si>
+  <si>
+    <t>LP-051931</t>
+  </si>
+  <si>
+    <t>LP-050538</t>
+  </si>
+  <si>
+    <t>LP-051375</t>
+  </si>
+  <si>
+    <t>LP-051409</t>
+  </si>
+  <si>
+    <t>LP-051498</t>
+  </si>
+  <si>
+    <t>LP-051501</t>
+  </si>
+  <si>
+    <t>LP-051502</t>
+  </si>
+  <si>
+    <t>LP-051506</t>
+  </si>
+  <si>
+    <t>LP-051507</t>
+  </si>
+  <si>
+    <t>LP-051601</t>
+  </si>
+  <si>
+    <t>LP-051603</t>
+  </si>
+  <si>
+    <t>LP-051604</t>
+  </si>
+  <si>
+    <t>LP-051605</t>
+  </si>
+  <si>
+    <t>LP-051664</t>
+  </si>
+  <si>
+    <t>LP-051665</t>
+  </si>
+  <si>
+    <t>LP-048389</t>
+  </si>
+  <si>
+    <t>LP-051626</t>
+  </si>
+  <si>
+    <t>LP-051658</t>
+  </si>
+  <si>
+    <t>LP-051756</t>
+  </si>
+  <si>
+    <t>LP-051575</t>
+  </si>
+  <si>
+    <t>LP-051617</t>
+  </si>
+  <si>
+    <t>LP-051618</t>
+  </si>
+  <si>
+    <t>LP-052135</t>
+  </si>
+  <si>
+    <t>LP-052011</t>
+  </si>
+  <si>
+    <t>LP-051606</t>
+  </si>
+  <si>
+    <t>LP-051609</t>
+  </si>
+  <si>
+    <t>LP-051627</t>
+  </si>
+  <si>
+    <t>LP-051656</t>
+  </si>
+  <si>
+    <t>LP-051659</t>
+  </si>
+  <si>
+    <t>LP-051686</t>
+  </si>
+  <si>
+    <t>LP-051687</t>
+  </si>
+  <si>
+    <t>LP-051736</t>
+  </si>
+  <si>
+    <t>LP-051753</t>
+  </si>
+  <si>
+    <t>LP-051754</t>
+  </si>
+  <si>
+    <t>LP-051902</t>
+  </si>
+  <si>
+    <t>LP-051930</t>
+  </si>
+  <si>
+    <t>LP-051966</t>
+  </si>
+  <si>
+    <t>LP-052076</t>
+  </si>
+  <si>
+    <t>LP-044151</t>
+  </si>
+  <si>
+    <t>LP-049891</t>
+  </si>
+  <si>
+    <t>LP-050304</t>
+  </si>
+  <si>
+    <t>LP-050501</t>
+  </si>
+  <si>
+    <t>LP-051494</t>
+  </si>
+  <si>
+    <t>LP-051495</t>
+  </si>
+  <si>
+    <t>LP-051599</t>
+  </si>
+  <si>
+    <t>LP-050001</t>
+  </si>
+  <si>
+    <t>LP-051497</t>
+  </si>
+  <si>
+    <t>LP-051680</t>
+  </si>
+  <si>
+    <t>LP-051682</t>
+  </si>
+  <si>
+    <t>LP-051683</t>
+  </si>
+  <si>
+    <t>LP-051685</t>
+  </si>
+  <si>
+    <t>LP-051709</t>
+  </si>
+  <si>
+    <t>LP-051745</t>
+  </si>
+  <si>
+    <t>LP-051746</t>
+  </si>
+  <si>
+    <t>LP-051749</t>
+  </si>
+  <si>
+    <t>LP-051750</t>
+  </si>
+  <si>
+    <t>LP-051883</t>
+  </si>
+  <si>
+    <t>LP-051884</t>
+  </si>
+  <si>
+    <t>LP-051887</t>
+  </si>
+  <si>
+    <t>LP-051903</t>
+  </si>
+  <si>
+    <t>LP-051904</t>
+  </si>
+  <si>
+    <t>LP-051905</t>
+  </si>
+  <si>
+    <t>LP-051906</t>
+  </si>
+  <si>
+    <t>LP-051907</t>
+  </si>
+  <si>
+    <t>LP-051908</t>
+  </si>
+  <si>
+    <t>LP-051909</t>
+  </si>
+  <si>
+    <t>LP-051910</t>
+  </si>
+  <si>
+    <t>LP-052008</t>
+  </si>
+  <si>
+    <t>LP-052009</t>
+  </si>
+  <si>
+    <t>LP-052017</t>
+  </si>
+  <si>
+    <t>LP-052018</t>
+  </si>
+  <si>
+    <t>LP-052153</t>
+  </si>
+  <si>
+    <t>LP-048713</t>
+  </si>
+  <si>
+    <t>LP-048714</t>
   </si>
   <si>
     <t>LP-047807</t>
-  </si>
-  <si>
-    <t>Possui linhas de compra e apontamento!</t>
   </si>
   <si>
     <t>LP-047806</t>
@@ -421,11 +676,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -440,72 +695,490 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
-        <v>11</v>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE29602-6ED9-4DF9-90AB-BC397FD3AFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84CCDE7-F2B9-44BD-A21E-EC56DAED4AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="96">
   <si>
     <t>LP</t>
   </si>
@@ -28,201 +28,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-050151</t>
-  </si>
-  <si>
-    <t>LP-050440</t>
-  </si>
-  <si>
-    <t>LP-050554</t>
-  </si>
-  <si>
-    <t>LP-050574</t>
-  </si>
-  <si>
-    <t>LP-050593</t>
-  </si>
-  <si>
-    <t>LP-050621</t>
-  </si>
-  <si>
-    <t>LP-050630</t>
-  </si>
-  <si>
-    <t>LP-051602</t>
-  </si>
-  <si>
-    <t>LP-050367</t>
-  </si>
-  <si>
-    <t>LP-050486</t>
-  </si>
-  <si>
-    <t>LP-050565</t>
-  </si>
-  <si>
-    <t>LP-051570</t>
-  </si>
-  <si>
-    <t>LP-051629</t>
-  </si>
-  <si>
-    <t>LP-051684</t>
-  </si>
-  <si>
-    <t>LP-051845</t>
-  </si>
-  <si>
-    <t>LP-051846</t>
-  </si>
-  <si>
-    <t>LP-051847</t>
-  </si>
-  <si>
-    <t>LP-051859</t>
-  </si>
-  <si>
-    <t>LP-051865</t>
-  </si>
-  <si>
-    <t>LP-051866</t>
-  </si>
-  <si>
-    <t>LP-051931</t>
-  </si>
-  <si>
-    <t>LP-050538</t>
-  </si>
-  <si>
-    <t>LP-051375</t>
-  </si>
-  <si>
-    <t>LP-051409</t>
-  </si>
-  <si>
-    <t>LP-051498</t>
-  </si>
-  <si>
-    <t>LP-051501</t>
-  </si>
-  <si>
-    <t>LP-051502</t>
-  </si>
-  <si>
-    <t>LP-051506</t>
-  </si>
-  <si>
-    <t>LP-051507</t>
-  </si>
-  <si>
-    <t>LP-051601</t>
-  </si>
-  <si>
-    <t>LP-051603</t>
-  </si>
-  <si>
-    <t>LP-051604</t>
-  </si>
-  <si>
-    <t>LP-051605</t>
-  </si>
-  <si>
-    <t>LP-051664</t>
-  </si>
-  <si>
-    <t>LP-051665</t>
-  </si>
-  <si>
-    <t>LP-048389</t>
-  </si>
-  <si>
-    <t>LP-051626</t>
-  </si>
-  <si>
-    <t>LP-051658</t>
-  </si>
-  <si>
-    <t>LP-051756</t>
-  </si>
-  <si>
-    <t>LP-051575</t>
-  </si>
-  <si>
-    <t>LP-051617</t>
-  </si>
-  <si>
-    <t>LP-051618</t>
-  </si>
-  <si>
-    <t>LP-052135</t>
-  </si>
-  <si>
-    <t>LP-052011</t>
-  </si>
-  <si>
-    <t>LP-051606</t>
-  </si>
-  <si>
-    <t>LP-051609</t>
-  </si>
-  <si>
-    <t>LP-051627</t>
-  </si>
-  <si>
-    <t>LP-051656</t>
-  </si>
-  <si>
-    <t>LP-051659</t>
-  </si>
-  <si>
-    <t>LP-051686</t>
-  </si>
-  <si>
-    <t>LP-051687</t>
-  </si>
-  <si>
-    <t>LP-051736</t>
-  </si>
-  <si>
-    <t>LP-051753</t>
-  </si>
-  <si>
-    <t>LP-051754</t>
-  </si>
-  <si>
-    <t>LP-051902</t>
-  </si>
-  <si>
-    <t>LP-051930</t>
-  </si>
-  <si>
-    <t>LP-051966</t>
-  </si>
-  <si>
-    <t>LP-052076</t>
-  </si>
-  <si>
-    <t>LP-044151</t>
-  </si>
-  <si>
-    <t>LP-049891</t>
-  </si>
-  <si>
-    <t>LP-050304</t>
-  </si>
-  <si>
-    <t>LP-050501</t>
-  </si>
-  <si>
-    <t>LP-051494</t>
-  </si>
-  <si>
-    <t>LP-051495</t>
-  </si>
-  <si>
-    <t>LP-051599</t>
-  </si>
-  <si>
     <t>LP-050001</t>
   </si>
   <si>
@@ -238,9 +43,6 @@
     <t>LP-051683</t>
   </si>
   <si>
-    <t>LP-051685</t>
-  </si>
-  <si>
     <t>LP-051709</t>
   </si>
   <si>
@@ -310,10 +112,202 @@
     <t>LP-048714</t>
   </si>
   <si>
-    <t>LP-047807</t>
-  </si>
-  <si>
-    <t>LP-047806</t>
+    <t>LP-039759</t>
+  </si>
+  <si>
+    <t>LP-040769</t>
+  </si>
+  <si>
+    <t>LP-047128</t>
+  </si>
+  <si>
+    <t>LP-047983</t>
+  </si>
+  <si>
+    <t>LP-049262</t>
+  </si>
+  <si>
+    <t>LP-049405</t>
+  </si>
+  <si>
+    <t>LP-049643</t>
+  </si>
+  <si>
+    <t>LP-049688</t>
+  </si>
+  <si>
+    <t>LP-050381</t>
+  </si>
+  <si>
+    <t>LP-050617</t>
+  </si>
+  <si>
+    <t>LP-051070</t>
+  </si>
+  <si>
+    <t>LP-051164</t>
+  </si>
+  <si>
+    <t>LP-051191</t>
+  </si>
+  <si>
+    <t>LP-051216</t>
+  </si>
+  <si>
+    <t>LP-051223</t>
+  </si>
+  <si>
+    <t>LP-051233</t>
+  </si>
+  <si>
+    <t>LP-051226</t>
+  </si>
+  <si>
+    <t>LP-051263</t>
+  </si>
+  <si>
+    <t>LP-051320</t>
+  </si>
+  <si>
+    <t>LP-051624</t>
+  </si>
+  <si>
+    <t>LP-051635</t>
+  </si>
+  <si>
+    <t>LP-052028</t>
+  </si>
+  <si>
+    <t>LP-052029</t>
+  </si>
+  <si>
+    <t>LP-052030</t>
+  </si>
+  <si>
+    <t>LP-052031</t>
+  </si>
+  <si>
+    <t>LP-052032</t>
+  </si>
+  <si>
+    <t>LP-052061</t>
+  </si>
+  <si>
+    <t>LP-052093</t>
+  </si>
+  <si>
+    <t>LP-052108</t>
+  </si>
+  <si>
+    <t>LP-052109</t>
+  </si>
+  <si>
+    <t>LP-052136</t>
+  </si>
+  <si>
+    <t>LP-052148</t>
+  </si>
+  <si>
+    <t>LP-052152</t>
+  </si>
+  <si>
+    <t>LP-052212</t>
+  </si>
+  <si>
+    <t>LP-052214</t>
+  </si>
+  <si>
+    <t>LP-052462</t>
+  </si>
+  <si>
+    <t>LP-052480</t>
+  </si>
+  <si>
+    <t>LP-052487</t>
+  </si>
+  <si>
+    <t>LP-052504</t>
+  </si>
+  <si>
+    <t>LP-052508</t>
+  </si>
+  <si>
+    <t>LP-052509</t>
+  </si>
+  <si>
+    <t>LP-052513</t>
+  </si>
+  <si>
+    <t>LP-052514</t>
+  </si>
+  <si>
+    <t>LP-052572</t>
+  </si>
+  <si>
+    <t>LP-052608</t>
+  </si>
+  <si>
+    <t>LP-052628</t>
+  </si>
+  <si>
+    <t>LP-052688</t>
+  </si>
+  <si>
+    <t>LP-052782</t>
+  </si>
+  <si>
+    <t>LP-052861</t>
+  </si>
+  <si>
+    <t>LP-052986</t>
+  </si>
+  <si>
+    <t>LP-045478</t>
+  </si>
+  <si>
+    <t>LP-045674</t>
+  </si>
+  <si>
+    <t>LP-048423</t>
+  </si>
+  <si>
+    <t>LP-049936</t>
+  </si>
+  <si>
+    <t>LP-050094</t>
+  </si>
+  <si>
+    <t>LP-050096</t>
+  </si>
+  <si>
+    <t>LP-050127</t>
+  </si>
+  <si>
+    <t>LP-050143</t>
+  </si>
+  <si>
+    <t>LP-050419</t>
+  </si>
+  <si>
+    <t>LP-051029</t>
+  </si>
+  <si>
+    <t>LP-051030</t>
+  </si>
+  <si>
+    <t>LP-051221</t>
+  </si>
+  <si>
+    <t>LP-051517</t>
+  </si>
+  <si>
+    <t>LP-051544</t>
+  </si>
+  <si>
+    <t>LP-051701</t>
+  </si>
+  <si>
+    <t>LP-052163</t>
   </si>
 </sst>
 </file>
@@ -676,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -693,417 +687,417 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
@@ -1169,16 +1163,6 @@
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84CCDE7-F2B9-44BD-A21E-EC56DAED4AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D021A0D4-ADC0-4F03-A3CC-1933DCC6C6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$48</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>LP</t>
   </si>
@@ -28,249 +31,111 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-050001</t>
-  </si>
-  <si>
-    <t>LP-051497</t>
-  </si>
-  <si>
-    <t>LP-051680</t>
-  </si>
-  <si>
-    <t>LP-051682</t>
-  </si>
-  <si>
-    <t>LP-051683</t>
-  </si>
-  <si>
-    <t>LP-051709</t>
-  </si>
-  <si>
-    <t>LP-051745</t>
-  </si>
-  <si>
-    <t>LP-051746</t>
-  </si>
-  <si>
-    <t>LP-051749</t>
-  </si>
-  <si>
-    <t>LP-051750</t>
-  </si>
-  <si>
-    <t>LP-051883</t>
-  </si>
-  <si>
-    <t>LP-051884</t>
-  </si>
-  <si>
-    <t>LP-051887</t>
-  </si>
-  <si>
-    <t>LP-051903</t>
-  </si>
-  <si>
-    <t>LP-051904</t>
-  </si>
-  <si>
-    <t>LP-051905</t>
-  </si>
-  <si>
-    <t>LP-051906</t>
-  </si>
-  <si>
-    <t>LP-051907</t>
-  </si>
-  <si>
-    <t>LP-051908</t>
-  </si>
-  <si>
-    <t>LP-051909</t>
-  </si>
-  <si>
-    <t>LP-051910</t>
-  </si>
-  <si>
-    <t>LP-052008</t>
-  </si>
-  <si>
-    <t>LP-052009</t>
-  </si>
-  <si>
-    <t>LP-052017</t>
-  </si>
-  <si>
     <t>LP-052018</t>
   </si>
   <si>
+    <t>LP-052028</t>
+  </si>
+  <si>
+    <t>LP-052029</t>
+  </si>
+  <si>
+    <t>LP-052030</t>
+  </si>
+  <si>
+    <t>LP-052031</t>
+  </si>
+  <si>
+    <t>LP-052032</t>
+  </si>
+  <si>
+    <t>LP-052061</t>
+  </si>
+  <si>
+    <t>LP-052093</t>
+  </si>
+  <si>
+    <t>LP-052108</t>
+  </si>
+  <si>
+    <t>LP-052109</t>
+  </si>
+  <si>
+    <t>LP-052136</t>
+  </si>
+  <si>
+    <t>LP-052148</t>
+  </si>
+  <si>
     <t>LP-052153</t>
   </si>
   <si>
+    <t>LP-052152</t>
+  </si>
+  <si>
+    <t>LP-052212</t>
+  </si>
+  <si>
+    <t>LP-052214</t>
+  </si>
+  <si>
+    <t>LP-052462</t>
+  </si>
+  <si>
+    <t>LP-052480</t>
+  </si>
+  <si>
+    <t>LP-052487</t>
+  </si>
+  <si>
+    <t>LP-052504</t>
+  </si>
+  <si>
+    <t>LP-052508</t>
+  </si>
+  <si>
+    <t>LP-052509</t>
+  </si>
+  <si>
+    <t>LP-052513</t>
+  </si>
+  <si>
+    <t>LP-052514</t>
+  </si>
+  <si>
+    <t>LP-052572</t>
+  </si>
+  <si>
+    <t>LP-052608</t>
+  </si>
+  <si>
+    <t>LP-052628</t>
+  </si>
+  <si>
+    <t>LP-052688</t>
+  </si>
+  <si>
+    <t>LP-052782</t>
+  </si>
+  <si>
+    <t>LP-052861</t>
+  </si>
+  <si>
+    <t>LP-045478</t>
+  </si>
+  <si>
+    <t>LP-045674</t>
+  </si>
+  <si>
+    <t>LP-048423</t>
+  </si>
+  <si>
     <t>LP-048713</t>
   </si>
   <si>
     <t>LP-048714</t>
   </si>
   <si>
-    <t>LP-039759</t>
-  </si>
-  <si>
-    <t>LP-040769</t>
-  </si>
-  <si>
-    <t>LP-047128</t>
-  </si>
-  <si>
-    <t>LP-047983</t>
-  </si>
-  <si>
-    <t>LP-049262</t>
-  </si>
-  <si>
-    <t>LP-049405</t>
-  </si>
-  <si>
-    <t>LP-049643</t>
-  </si>
-  <si>
-    <t>LP-049688</t>
-  </si>
-  <si>
-    <t>LP-050381</t>
-  </si>
-  <si>
-    <t>LP-050617</t>
-  </si>
-  <si>
-    <t>LP-051070</t>
-  </si>
-  <si>
-    <t>LP-051164</t>
-  </si>
-  <si>
-    <t>LP-051191</t>
-  </si>
-  <si>
-    <t>LP-051216</t>
-  </si>
-  <si>
-    <t>LP-051223</t>
-  </si>
-  <si>
-    <t>LP-051233</t>
-  </si>
-  <si>
-    <t>LP-051226</t>
-  </si>
-  <si>
-    <t>LP-051263</t>
-  </si>
-  <si>
-    <t>LP-051320</t>
-  </si>
-  <si>
-    <t>LP-051624</t>
-  </si>
-  <si>
-    <t>LP-051635</t>
-  </si>
-  <si>
-    <t>LP-052028</t>
-  </si>
-  <si>
-    <t>LP-052029</t>
-  </si>
-  <si>
-    <t>LP-052030</t>
-  </si>
-  <si>
-    <t>LP-052031</t>
-  </si>
-  <si>
-    <t>LP-052032</t>
-  </si>
-  <si>
-    <t>LP-052061</t>
-  </si>
-  <si>
-    <t>LP-052093</t>
-  </si>
-  <si>
-    <t>LP-052108</t>
-  </si>
-  <si>
-    <t>LP-052109</t>
-  </si>
-  <si>
-    <t>LP-052136</t>
-  </si>
-  <si>
-    <t>LP-052148</t>
-  </si>
-  <si>
-    <t>LP-052152</t>
-  </si>
-  <si>
-    <t>LP-052212</t>
-  </si>
-  <si>
-    <t>LP-052214</t>
-  </si>
-  <si>
-    <t>LP-052462</t>
-  </si>
-  <si>
-    <t>LP-052480</t>
-  </si>
-  <si>
-    <t>LP-052487</t>
-  </si>
-  <si>
-    <t>LP-052504</t>
-  </si>
-  <si>
-    <t>LP-052508</t>
-  </si>
-  <si>
-    <t>LP-052509</t>
-  </si>
-  <si>
-    <t>LP-052513</t>
-  </si>
-  <si>
-    <t>LP-052514</t>
-  </si>
-  <si>
-    <t>LP-052572</t>
-  </si>
-  <si>
-    <t>LP-052608</t>
-  </si>
-  <si>
-    <t>LP-052628</t>
-  </si>
-  <si>
-    <t>LP-052688</t>
-  </si>
-  <si>
-    <t>LP-052782</t>
-  </si>
-  <si>
-    <t>LP-052861</t>
-  </si>
-  <si>
-    <t>LP-052986</t>
-  </si>
-  <si>
-    <t>LP-045478</t>
-  </si>
-  <si>
-    <t>LP-045674</t>
-  </si>
-  <si>
-    <t>LP-048423</t>
-  </si>
-  <si>
     <t>LP-049936</t>
   </si>
   <si>
@@ -299,12 +164,6 @@
   </si>
   <si>
     <t>LP-051517</t>
-  </si>
-  <si>
-    <t>LP-051544</t>
-  </si>
-  <si>
-    <t>LP-051701</t>
   </si>
   <si>
     <t>LP-052163</t>
@@ -670,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -687,482 +546,237 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D021A0D4-ADC0-4F03-A3CC-1933DCC6C6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16D1895-7DCF-4C1F-BAF6-E22EDE7DF2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$48</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
   <si>
     <t>LP</t>
   </si>
@@ -31,142 +28,232 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-052018</t>
-  </si>
-  <si>
-    <t>LP-052028</t>
-  </si>
-  <si>
-    <t>LP-052029</t>
-  </si>
-  <si>
-    <t>LP-052030</t>
-  </si>
-  <si>
-    <t>LP-052031</t>
-  </si>
-  <si>
-    <t>LP-052032</t>
-  </si>
-  <si>
-    <t>LP-052061</t>
-  </si>
-  <si>
-    <t>LP-052093</t>
-  </si>
-  <si>
-    <t>LP-052108</t>
-  </si>
-  <si>
-    <t>LP-052109</t>
-  </si>
-  <si>
-    <t>LP-052136</t>
-  </si>
-  <si>
-    <t>LP-052148</t>
-  </si>
-  <si>
-    <t>LP-052153</t>
-  </si>
-  <si>
-    <t>LP-052152</t>
-  </si>
-  <si>
-    <t>LP-052212</t>
-  </si>
-  <si>
-    <t>LP-052214</t>
-  </si>
-  <si>
-    <t>LP-052462</t>
-  </si>
-  <si>
-    <t>LP-052480</t>
-  </si>
-  <si>
-    <t>LP-052487</t>
-  </si>
-  <si>
-    <t>LP-052504</t>
-  </si>
-  <si>
-    <t>LP-052508</t>
-  </si>
-  <si>
-    <t>LP-052509</t>
-  </si>
-  <si>
-    <t>LP-052513</t>
-  </si>
-  <si>
-    <t>LP-052514</t>
-  </si>
-  <si>
-    <t>LP-052572</t>
-  </si>
-  <si>
-    <t>LP-052608</t>
-  </si>
-  <si>
-    <t>LP-052628</t>
+    <t>LP-051547</t>
+  </si>
+  <si>
+    <t>LP-051590</t>
+  </si>
+  <si>
+    <t>LP-051773</t>
+  </si>
+  <si>
+    <t>LP-051896</t>
+  </si>
+  <si>
+    <t>LP-051897</t>
+  </si>
+  <si>
+    <t>LP-051898</t>
+  </si>
+  <si>
+    <t>LP-051920</t>
+  </si>
+  <si>
+    <t>LP-051921</t>
+  </si>
+  <si>
+    <t>LP-052027</t>
+  </si>
+  <si>
+    <t>LP-052033</t>
+  </si>
+  <si>
+    <t>LP-052143</t>
+  </si>
+  <si>
+    <t>LP-052144</t>
+  </si>
+  <si>
+    <t>LP-052305</t>
+  </si>
+  <si>
+    <t>LP-052425</t>
+  </si>
+  <si>
+    <t>LP-052428</t>
+  </si>
+  <si>
+    <t>LP-052532</t>
+  </si>
+  <si>
+    <t>LP-052565</t>
+  </si>
+  <si>
+    <t>LP-052566</t>
+  </si>
+  <si>
+    <t>LP-052567</t>
+  </si>
+  <si>
+    <t>LP-052582</t>
+  </si>
+  <si>
+    <t>LP-052593</t>
+  </si>
+  <si>
+    <t>LP-052594</t>
+  </si>
+  <si>
+    <t>LP-052605</t>
+  </si>
+  <si>
+    <t>LP-052606</t>
+  </si>
+  <si>
+    <t>LP-052607</t>
+  </si>
+  <si>
+    <t>LP-052638</t>
+  </si>
+  <si>
+    <t>LP-052673</t>
+  </si>
+  <si>
+    <t>LP-052685</t>
+  </si>
+  <si>
+    <t>LP-052686</t>
   </si>
   <si>
     <t>LP-052688</t>
   </si>
   <si>
-    <t>LP-052782</t>
-  </si>
-  <si>
-    <t>LP-052861</t>
-  </si>
-  <si>
-    <t>LP-045478</t>
-  </si>
-  <si>
-    <t>LP-045674</t>
-  </si>
-  <si>
-    <t>LP-048423</t>
-  </si>
-  <si>
-    <t>LP-048713</t>
-  </si>
-  <si>
-    <t>LP-048714</t>
-  </si>
-  <si>
-    <t>LP-049936</t>
-  </si>
-  <si>
-    <t>LP-050094</t>
-  </si>
-  <si>
-    <t>LP-050096</t>
-  </si>
-  <si>
-    <t>LP-050127</t>
-  </si>
-  <si>
-    <t>LP-050143</t>
-  </si>
-  <si>
-    <t>LP-050419</t>
-  </si>
-  <si>
-    <t>LP-051029</t>
-  </si>
-  <si>
-    <t>LP-051030</t>
-  </si>
-  <si>
-    <t>LP-051221</t>
-  </si>
-  <si>
-    <t>LP-051517</t>
-  </si>
-  <si>
-    <t>LP-052163</t>
+    <t>LP-052718</t>
+  </si>
+  <si>
+    <t>LP-052777</t>
+  </si>
+  <si>
+    <t>LP-052824</t>
+  </si>
+  <si>
+    <t>LP-052927</t>
+  </si>
+  <si>
+    <t>LP-053000</t>
+  </si>
+  <si>
+    <t>LP-053131</t>
+  </si>
+  <si>
+    <t>LP-053150</t>
+  </si>
+  <si>
+    <t>LP-053166</t>
+  </si>
+  <si>
+    <t>LP-053279</t>
+  </si>
+  <si>
+    <t>LP-049001</t>
+  </si>
+  <si>
+    <t>LP-049049</t>
+  </si>
+  <si>
+    <t>LP-049156</t>
+  </si>
+  <si>
+    <t>LP-049495</t>
+  </si>
+  <si>
+    <t>LP-049506</t>
+  </si>
+  <si>
+    <t>LP-049839</t>
+  </si>
+  <si>
+    <t>LP-049937</t>
+  </si>
+  <si>
+    <t>LP-049966</t>
+  </si>
+  <si>
+    <t>LP-050135</t>
+  </si>
+  <si>
+    <t>LP-050228</t>
+  </si>
+  <si>
+    <t>LP-050311</t>
+  </si>
+  <si>
+    <t>LP-050398</t>
+  </si>
+  <si>
+    <t>LP-050408</t>
+  </si>
+  <si>
+    <t>LP-050605</t>
+  </si>
+  <si>
+    <t>LP-050663</t>
+  </si>
+  <si>
+    <t>LP-050718</t>
+  </si>
+  <si>
+    <t>LP-051028</t>
+  </si>
+  <si>
+    <t>LP-051376</t>
+  </si>
+  <si>
+    <t>LP-051486</t>
+  </si>
+  <si>
+    <t>LP-051518</t>
+  </si>
+  <si>
+    <t>LP-051700</t>
+  </si>
+  <si>
+    <t>LP-051714</t>
+  </si>
+  <si>
+    <t>LP-051723</t>
+  </si>
+  <si>
+    <t>LP-051777</t>
+  </si>
+  <si>
+    <t>LP-052125</t>
+  </si>
+  <si>
+    <t>LP-052126</t>
+  </si>
+  <si>
+    <t>LP-052127</t>
+  </si>
+  <si>
+    <t>LP-052139</t>
+  </si>
+  <si>
+    <t>LP-052200</t>
+  </si>
+  <si>
+    <t>LP-052226</t>
+  </si>
+  <si>
+    <t>LP-052380</t>
+  </si>
+  <si>
+    <t>LP-052401</t>
+  </si>
+  <si>
+    <t>LP-052403</t>
+  </si>
+  <si>
+    <t>LP-052404</t>
+  </si>
+  <si>
+    <t>LP-052405</t>
+  </si>
+  <si>
+    <t>LP-052549</t>
+  </si>
+  <si>
+    <t>LP-052753</t>
   </si>
 </sst>
 </file>
@@ -529,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -646,52 +733,52 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -711,72 +798,227 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780DDC42-CBE4-4473-9C33-9DB0BB1CACD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0FB4C0-5B89-4B51-8303-A40FC5FAAC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>LP</t>
   </si>
@@ -28,25 +28,355 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-051723</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-052380</t>
-  </si>
-  <si>
-    <t>LP-052405</t>
-  </si>
-  <si>
-    <t>LP-052549</t>
-  </si>
-  <si>
-    <t>LP-052753</t>
-  </si>
-  <si>
-    <t>LP-051176</t>
+    <t>LP-037673</t>
+  </si>
+  <si>
+    <t>LP-044152</t>
+  </si>
+  <si>
+    <t>LP-046515</t>
+  </si>
+  <si>
+    <t>LP-047285</t>
+  </si>
+  <si>
+    <t>LP-048572</t>
+  </si>
+  <si>
+    <t>LP-049073</t>
+  </si>
+  <si>
+    <t>LP-050273</t>
+  </si>
+  <si>
+    <t>LP-050978</t>
+  </si>
+  <si>
+    <t>LP-051199</t>
+  </si>
+  <si>
+    <t>LP-051216</t>
+  </si>
+  <si>
+    <t>LP-051380</t>
+  </si>
+  <si>
+    <t>LP-051419</t>
+  </si>
+  <si>
+    <t>LP-051511</t>
+  </si>
+  <si>
+    <t>LP-051607</t>
+  </si>
+  <si>
+    <t>LP-051608</t>
+  </si>
+  <si>
+    <t>LP-052184</t>
+  </si>
+  <si>
+    <t>LP-052206</t>
+  </si>
+  <si>
+    <t>LP-052262</t>
+  </si>
+  <si>
+    <t>LP-053323</t>
+  </si>
+  <si>
+    <t>LP-053346</t>
+  </si>
+  <si>
+    <t>LP-053349</t>
+  </si>
+  <si>
+    <t>LP-053392</t>
+  </si>
+  <si>
+    <t>LP-053435</t>
+  </si>
+  <si>
+    <t>LP-053527</t>
+  </si>
+  <si>
+    <t>LP-048143</t>
+  </si>
+  <si>
+    <t>LP-048172</t>
+  </si>
+  <si>
+    <t>LP-048199</t>
+  </si>
+  <si>
+    <t>LP-049316</t>
+  </si>
+  <si>
+    <t>LP-049318</t>
+  </si>
+  <si>
+    <t>LP-049325</t>
+  </si>
+  <si>
+    <t>LP-049452</t>
+  </si>
+  <si>
+    <t>LP-049461</t>
+  </si>
+  <si>
+    <t>LP-049647</t>
+  </si>
+  <si>
+    <t>LP-049709</t>
+  </si>
+  <si>
+    <t>LP-049932</t>
+  </si>
+  <si>
+    <t>LP-049953</t>
+  </si>
+  <si>
+    <t>LP-050132</t>
+  </si>
+  <si>
+    <t>LP-050244</t>
+  </si>
+  <si>
+    <t>LP-050317</t>
+  </si>
+  <si>
+    <t>LP-050404</t>
+  </si>
+  <si>
+    <t>LP-050410</t>
+  </si>
+  <si>
+    <t>LP-050429</t>
+  </si>
+  <si>
+    <t>LP-050430</t>
+  </si>
+  <si>
+    <t>LP-050456</t>
+  </si>
+  <si>
+    <t>LP-050460</t>
+  </si>
+  <si>
+    <t>LP-050461</t>
+  </si>
+  <si>
+    <t>LP-050465</t>
+  </si>
+  <si>
+    <t>LP-050466</t>
+  </si>
+  <si>
+    <t>LP-050468</t>
+  </si>
+  <si>
+    <t>LP-050469</t>
+  </si>
+  <si>
+    <t>LP-050479</t>
+  </si>
+  <si>
+    <t>LP-050529</t>
+  </si>
+  <si>
+    <t>LP-050731</t>
+  </si>
+  <si>
+    <t>LP-050736</t>
+  </si>
+  <si>
+    <t>LP-050753</t>
+  </si>
+  <si>
+    <t>LP-050855</t>
+  </si>
+  <si>
+    <t>LP-050856</t>
+  </si>
+  <si>
+    <t>LP-051019</t>
+  </si>
+  <si>
+    <t>LP-051042</t>
+  </si>
+  <si>
+    <t>LP-051069</t>
+  </si>
+  <si>
+    <t>LP-051097</t>
+  </si>
+  <si>
+    <t>LP-051217</t>
+  </si>
+  <si>
+    <t>LP-051220</t>
+  </si>
+  <si>
+    <t>LP-051281</t>
+  </si>
+  <si>
+    <t>LP-051284</t>
+  </si>
+  <si>
+    <t>LP-051297</t>
+  </si>
+  <si>
+    <t>LP-051353</t>
+  </si>
+  <si>
+    <t>LP-051369</t>
+  </si>
+  <si>
+    <t>LP-051388</t>
+  </si>
+  <si>
+    <t>LP-051391</t>
+  </si>
+  <si>
+    <t>LP-051395</t>
+  </si>
+  <si>
+    <t>LP-051425</t>
+  </si>
+  <si>
+    <t>LP-051431</t>
+  </si>
+  <si>
+    <t>LP-051432</t>
+  </si>
+  <si>
+    <t>LP-051434</t>
+  </si>
+  <si>
+    <t>LP-051448</t>
+  </si>
+  <si>
+    <t>LP-051449</t>
+  </si>
+  <si>
+    <t>LP-051519</t>
+  </si>
+  <si>
+    <t>LP-051540</t>
+  </si>
+  <si>
+    <t>LP-051541</t>
+  </si>
+  <si>
+    <t>LP-051543</t>
+  </si>
+  <si>
+    <t>LP-051705</t>
+  </si>
+  <si>
+    <t>LP-051712</t>
+  </si>
+  <si>
+    <t>LP-051716</t>
+  </si>
+  <si>
+    <t>LP-052122</t>
+  </si>
+  <si>
+    <t>LP-052138</t>
+  </si>
+  <si>
+    <t>LP-052141</t>
+  </si>
+  <si>
+    <t>LP-052160</t>
+  </si>
+  <si>
+    <t>LP-052199</t>
+  </si>
+  <si>
+    <t>LP-052308</t>
+  </si>
+  <si>
+    <t>LP-052309</t>
+  </si>
+  <si>
+    <t>LP-052311</t>
+  </si>
+  <si>
+    <t>LP-052312</t>
+  </si>
+  <si>
+    <t>LP-052326</t>
+  </si>
+  <si>
+    <t>LP-052372</t>
+  </si>
+  <si>
+    <t>LP-052381</t>
+  </si>
+  <si>
+    <t>LP-052386</t>
+  </si>
+  <si>
+    <t>LP-052400</t>
+  </si>
+  <si>
+    <t>LP-052406</t>
+  </si>
+  <si>
+    <t>LP-052623</t>
+  </si>
+  <si>
+    <t>LP-052680</t>
+  </si>
+  <si>
+    <t>LP-052681</t>
+  </si>
+  <si>
+    <t>LP-052720</t>
+  </si>
+  <si>
+    <t>LP-052721</t>
+  </si>
+  <si>
+    <t>LP-052722</t>
+  </si>
+  <si>
+    <t>LP-052726</t>
+  </si>
+  <si>
+    <t>LP-052727</t>
+  </si>
+  <si>
+    <t>LP-052728</t>
+  </si>
+  <si>
+    <t>LP-052729</t>
+  </si>
+  <si>
+    <t>LP-052749</t>
+  </si>
+  <si>
+    <t>LP-052752</t>
+  </si>
+  <si>
+    <t>LP-052754</t>
+  </si>
+  <si>
+    <t>LP-052756</t>
+  </si>
+  <si>
+    <t>LP-052773</t>
+  </si>
+  <si>
+    <t>LP-052978</t>
+  </si>
+  <si>
+    <t>LP-053040</t>
+  </si>
+  <si>
+    <t>LP-053105</t>
   </si>
 </sst>
 </file>
@@ -409,11 +739,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -428,48 +758,585 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
-        <v>3</v>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16D1895-7DCF-4C1F-BAF6-E22EDE7DF2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF4F87-A023-4599-8139-4D0D218A836C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
   <si>
     <t>LP</t>
   </si>
@@ -28,232 +28,181 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-051547</t>
-  </si>
-  <si>
-    <t>LP-051590</t>
-  </si>
-  <si>
-    <t>LP-051773</t>
-  </si>
-  <si>
-    <t>LP-051896</t>
-  </si>
-  <si>
-    <t>LP-051897</t>
-  </si>
-  <si>
-    <t>LP-051898</t>
-  </si>
-  <si>
-    <t>LP-051920</t>
-  </si>
-  <si>
-    <t>LP-051921</t>
-  </si>
-  <si>
-    <t>LP-052027</t>
-  </si>
-  <si>
-    <t>LP-052033</t>
-  </si>
-  <si>
-    <t>LP-052143</t>
-  </si>
-  <si>
-    <t>LP-052144</t>
-  </si>
-  <si>
-    <t>LP-052305</t>
-  </si>
-  <si>
-    <t>LP-052425</t>
-  </si>
-  <si>
-    <t>LP-052428</t>
-  </si>
-  <si>
-    <t>LP-052532</t>
-  </si>
-  <si>
-    <t>LP-052565</t>
-  </si>
-  <si>
-    <t>LP-052566</t>
-  </si>
-  <si>
-    <t>LP-052567</t>
-  </si>
-  <si>
-    <t>LP-052582</t>
-  </si>
-  <si>
-    <t>LP-052593</t>
-  </si>
-  <si>
-    <t>LP-052594</t>
-  </si>
-  <si>
-    <t>LP-052605</t>
-  </si>
-  <si>
-    <t>LP-052606</t>
-  </si>
-  <si>
-    <t>LP-052607</t>
-  </si>
-  <si>
-    <t>LP-052638</t>
-  </si>
-  <si>
-    <t>LP-052673</t>
-  </si>
-  <si>
-    <t>LP-052685</t>
-  </si>
-  <si>
-    <t>LP-052686</t>
-  </si>
-  <si>
-    <t>LP-052688</t>
-  </si>
-  <si>
-    <t>LP-052718</t>
-  </si>
-  <si>
-    <t>LP-052777</t>
-  </si>
-  <si>
-    <t>LP-052824</t>
-  </si>
-  <si>
-    <t>LP-052927</t>
-  </si>
-  <si>
-    <t>LP-053000</t>
-  </si>
-  <si>
-    <t>LP-053131</t>
-  </si>
-  <si>
-    <t>LP-053150</t>
-  </si>
-  <si>
-    <t>LP-053166</t>
-  </si>
-  <si>
-    <t>LP-053279</t>
-  </si>
-  <si>
-    <t>LP-049001</t>
-  </si>
-  <si>
-    <t>LP-049049</t>
-  </si>
-  <si>
-    <t>LP-049156</t>
-  </si>
-  <si>
-    <t>LP-049495</t>
-  </si>
-  <si>
-    <t>LP-049506</t>
-  </si>
-  <si>
-    <t>LP-049839</t>
-  </si>
-  <si>
-    <t>LP-049937</t>
-  </si>
-  <si>
-    <t>LP-049966</t>
-  </si>
-  <si>
-    <t>LP-050135</t>
-  </si>
-  <si>
-    <t>LP-050228</t>
-  </si>
-  <si>
-    <t>LP-050311</t>
-  </si>
-  <si>
-    <t>LP-050398</t>
-  </si>
-  <si>
-    <t>LP-050408</t>
-  </si>
-  <si>
-    <t>LP-050605</t>
-  </si>
-  <si>
-    <t>LP-050663</t>
-  </si>
-  <si>
-    <t>LP-050718</t>
-  </si>
-  <si>
-    <t>LP-051028</t>
-  </si>
-  <si>
-    <t>LP-051376</t>
-  </si>
-  <si>
-    <t>LP-051486</t>
-  </si>
-  <si>
-    <t>LP-051518</t>
-  </si>
-  <si>
-    <t>LP-051700</t>
-  </si>
-  <si>
-    <t>LP-051714</t>
-  </si>
-  <si>
-    <t>LP-051723</t>
-  </si>
-  <si>
-    <t>LP-051777</t>
-  </si>
-  <si>
-    <t>LP-052125</t>
-  </si>
-  <si>
-    <t>LP-052126</t>
-  </si>
-  <si>
-    <t>LP-052127</t>
-  </si>
-  <si>
-    <t>LP-052139</t>
-  </si>
-  <si>
-    <t>LP-052200</t>
-  </si>
-  <si>
-    <t>LP-052226</t>
-  </si>
-  <si>
-    <t>LP-052380</t>
-  </si>
-  <si>
-    <t>LP-052401</t>
-  </si>
-  <si>
-    <t>LP-052403</t>
-  </si>
-  <si>
-    <t>LP-052404</t>
-  </si>
-  <si>
-    <t>LP-052405</t>
-  </si>
-  <si>
-    <t>LP-052549</t>
-  </si>
-  <si>
-    <t>LP-052753</t>
+    <t>LP-050367</t>
+  </si>
+  <si>
+    <t>LP-051658</t>
+  </si>
+  <si>
+    <t>LP-051756</t>
+  </si>
+  <si>
+    <t>LP-051575</t>
+  </si>
+  <si>
+    <t>LP-051617</t>
+  </si>
+  <si>
+    <t>LP-051618</t>
+  </si>
+  <si>
+    <t>LP-052135</t>
+  </si>
+  <si>
+    <t>LP-052011</t>
+  </si>
+  <si>
+    <t>LP-051606</t>
+  </si>
+  <si>
+    <t>LP-051609</t>
+  </si>
+  <si>
+    <t>LP-051627</t>
+  </si>
+  <si>
+    <t>LP-051656</t>
+  </si>
+  <si>
+    <t>LP-051659</t>
+  </si>
+  <si>
+    <t>LP-051686</t>
+  </si>
+  <si>
+    <t>LP-051687</t>
+  </si>
+  <si>
+    <t>LP-051736</t>
+  </si>
+  <si>
+    <t>LP-051754</t>
+  </si>
+  <si>
+    <t>LP-051902</t>
+  </si>
+  <si>
+    <t>LP-051930</t>
+  </si>
+  <si>
+    <t>LP-051966</t>
+  </si>
+  <si>
+    <t>LP-052076</t>
+  </si>
+  <si>
+    <t>LP-044151</t>
+  </si>
+  <si>
+    <t>LP-049891</t>
+  </si>
+  <si>
+    <t>LP-050304</t>
+  </si>
+  <si>
+    <t>LP-050501</t>
+  </si>
+  <si>
+    <t>LP-051494</t>
+  </si>
+  <si>
+    <t>LP-051495</t>
+  </si>
+  <si>
+    <t>LP-051599</t>
+  </si>
+  <si>
+    <t>LP-050001</t>
+  </si>
+  <si>
+    <t>LP-051497</t>
+  </si>
+  <si>
+    <t>LP-051680</t>
+  </si>
+  <si>
+    <t>LP-051682</t>
+  </si>
+  <si>
+    <t>LP-051683</t>
+  </si>
+  <si>
+    <t>LP-051685</t>
+  </si>
+  <si>
+    <t>LP-051709</t>
+  </si>
+  <si>
+    <t>LP-051745</t>
+  </si>
+  <si>
+    <t>LP-051746</t>
+  </si>
+  <si>
+    <t>LP-051749</t>
+  </si>
+  <si>
+    <t>LP-051750</t>
+  </si>
+  <si>
+    <t>LP-051883</t>
+  </si>
+  <si>
+    <t>LP-051884</t>
+  </si>
+  <si>
+    <t>LP-051887</t>
+  </si>
+  <si>
+    <t>LP-051903</t>
+  </si>
+  <si>
+    <t>LP-051904</t>
+  </si>
+  <si>
+    <t>LP-051905</t>
+  </si>
+  <si>
+    <t>LP-051906</t>
+  </si>
+  <si>
+    <t>LP-051907</t>
+  </si>
+  <si>
+    <t>LP-051908</t>
+  </si>
+  <si>
+    <t>LP-051909</t>
+  </si>
+  <si>
+    <t>LP-051910</t>
+  </si>
+  <si>
+    <t>LP-052008</t>
+  </si>
+  <si>
+    <t>LP-052009</t>
+  </si>
+  <si>
+    <t>LP-052017</t>
+  </si>
+  <si>
+    <t>LP-052018</t>
+  </si>
+  <si>
+    <t>LP-052153</t>
+  </si>
+  <si>
+    <t>LP-048713</t>
+  </si>
+  <si>
+    <t>LP-048714</t>
+  </si>
+  <si>
+    <t>LP-047807</t>
+  </si>
+  <si>
+    <t>LP-047806</t>
   </si>
 </sst>
 </file>
@@ -616,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -633,207 +582,207 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -843,182 +792,92 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0FB4C0-5B89-4B51-8303-A40FC5FAAC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB29296-69C2-4EF9-8881-3AD34CD8C766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,213 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>LP</t>
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>LP-037673</t>
-  </si>
-  <si>
-    <t>LP-044152</t>
-  </si>
-  <si>
-    <t>LP-046515</t>
-  </si>
-  <si>
-    <t>LP-047285</t>
-  </si>
-  <si>
-    <t>LP-048572</t>
-  </si>
-  <si>
-    <t>LP-049073</t>
-  </si>
-  <si>
-    <t>LP-050273</t>
-  </si>
-  <si>
-    <t>LP-050978</t>
-  </si>
-  <si>
-    <t>LP-051199</t>
-  </si>
-  <si>
-    <t>LP-051216</t>
-  </si>
-  <si>
-    <t>LP-051380</t>
-  </si>
-  <si>
-    <t>LP-051419</t>
-  </si>
-  <si>
-    <t>LP-051511</t>
-  </si>
-  <si>
-    <t>LP-051607</t>
-  </si>
-  <si>
-    <t>LP-051608</t>
-  </si>
-  <si>
-    <t>LP-052184</t>
-  </si>
-  <si>
-    <t>LP-052206</t>
-  </si>
-  <si>
-    <t>LP-052262</t>
-  </si>
-  <si>
-    <t>LP-053323</t>
-  </si>
-  <si>
-    <t>LP-053346</t>
-  </si>
-  <si>
-    <t>LP-053349</t>
-  </si>
-  <si>
-    <t>LP-053392</t>
-  </si>
-  <si>
-    <t>LP-053435</t>
-  </si>
-  <si>
-    <t>LP-053527</t>
-  </si>
-  <si>
-    <t>LP-048143</t>
-  </si>
-  <si>
-    <t>LP-048172</t>
-  </si>
-  <si>
-    <t>LP-048199</t>
-  </si>
-  <si>
-    <t>LP-049316</t>
-  </si>
-  <si>
-    <t>LP-049318</t>
-  </si>
-  <si>
-    <t>LP-049325</t>
-  </si>
-  <si>
-    <t>LP-049452</t>
-  </si>
-  <si>
-    <t>LP-049461</t>
-  </si>
-  <si>
-    <t>LP-049647</t>
-  </si>
-  <si>
-    <t>LP-049709</t>
-  </si>
-  <si>
-    <t>LP-049932</t>
-  </si>
-  <si>
-    <t>LP-049953</t>
-  </si>
-  <si>
-    <t>LP-050132</t>
-  </si>
-  <si>
-    <t>LP-050244</t>
-  </si>
-  <si>
-    <t>LP-050317</t>
-  </si>
-  <si>
-    <t>LP-050404</t>
-  </si>
-  <si>
-    <t>LP-050410</t>
-  </si>
-  <si>
-    <t>LP-050429</t>
-  </si>
-  <si>
-    <t>LP-050430</t>
-  </si>
-  <si>
-    <t>LP-050456</t>
-  </si>
-  <si>
-    <t>LP-050460</t>
-  </si>
-  <si>
-    <t>LP-050461</t>
-  </si>
-  <si>
-    <t>LP-050465</t>
-  </si>
-  <si>
-    <t>LP-050466</t>
-  </si>
-  <si>
-    <t>LP-050468</t>
-  </si>
-  <si>
-    <t>LP-050469</t>
-  </si>
-  <si>
-    <t>LP-050479</t>
-  </si>
-  <si>
-    <t>LP-050529</t>
-  </si>
-  <si>
-    <t>LP-050731</t>
-  </si>
-  <si>
-    <t>LP-050736</t>
-  </si>
-  <si>
-    <t>LP-050753</t>
-  </si>
-  <si>
-    <t>LP-050855</t>
-  </si>
-  <si>
-    <t>LP-050856</t>
-  </si>
-  <si>
-    <t>LP-051019</t>
-  </si>
-  <si>
-    <t>LP-051042</t>
-  </si>
-  <si>
-    <t>LP-051069</t>
-  </si>
-  <si>
-    <t>LP-051097</t>
-  </si>
-  <si>
-    <t>LP-051217</t>
-  </si>
-  <si>
-    <t>LP-051220</t>
-  </si>
-  <si>
-    <t>LP-051281</t>
-  </si>
-  <si>
-    <t>LP-051284</t>
-  </si>
-  <si>
-    <t>LP-051297</t>
-  </si>
-  <si>
-    <t>LP-051353</t>
   </si>
   <si>
     <t>LP-051369</t>
@@ -739,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1004,341 +803,6 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>118</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF4F87-A023-4599-8139-4D0D218A836C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F4EF6F-954F-4951-86D3-04D22F3ECA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>LP</t>
   </si>
@@ -28,76 +28,46 @@
     <t>Status</t>
   </si>
   <si>
+    <t>LP-051656</t>
+  </si>
+  <si>
+    <t>LP-051659</t>
+  </si>
+  <si>
+    <t>LP-051686</t>
+  </si>
+  <si>
+    <t>LP-051687</t>
+  </si>
+  <si>
+    <t>LP-051736</t>
+  </si>
+  <si>
+    <t>LP-051754</t>
+  </si>
+  <si>
+    <t>LP-051902</t>
+  </si>
+  <si>
+    <t>LP-051930</t>
+  </si>
+  <si>
+    <t>LP-051966</t>
+  </si>
+  <si>
+    <t>LP-052076</t>
+  </si>
+  <si>
+    <t>LP-044151</t>
+  </si>
+  <si>
+    <t>LP-049891</t>
+  </si>
+  <si>
+    <t>LP-050304</t>
+  </si>
+  <si>
     <t>LP-050367</t>
-  </si>
-  <si>
-    <t>LP-051658</t>
-  </si>
-  <si>
-    <t>LP-051756</t>
-  </si>
-  <si>
-    <t>LP-051575</t>
-  </si>
-  <si>
-    <t>LP-051617</t>
-  </si>
-  <si>
-    <t>LP-051618</t>
-  </si>
-  <si>
-    <t>LP-052135</t>
-  </si>
-  <si>
-    <t>LP-052011</t>
-  </si>
-  <si>
-    <t>LP-051606</t>
-  </si>
-  <si>
-    <t>LP-051609</t>
-  </si>
-  <si>
-    <t>LP-051627</t>
-  </si>
-  <si>
-    <t>LP-051656</t>
-  </si>
-  <si>
-    <t>LP-051659</t>
-  </si>
-  <si>
-    <t>LP-051686</t>
-  </si>
-  <si>
-    <t>LP-051687</t>
-  </si>
-  <si>
-    <t>LP-051736</t>
-  </si>
-  <si>
-    <t>LP-051754</t>
-  </si>
-  <si>
-    <t>LP-051902</t>
-  </si>
-  <si>
-    <t>LP-051930</t>
-  </si>
-  <si>
-    <t>LP-051966</t>
-  </si>
-  <si>
-    <t>LP-052076</t>
-  </si>
-  <si>
-    <t>LP-044151</t>
-  </si>
-  <si>
-    <t>LP-049891</t>
-  </si>
-  <si>
-    <t>LP-050304</t>
   </si>
   <si>
     <t>LP-050501</t>
@@ -565,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -582,122 +552,122 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -737,57 +707,57 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
@@ -828,56 +798,6 @@
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F4EF6F-954F-4951-86D3-04D22F3ECA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A606882-FE57-43EA-BD8B-4758FD261AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
   <si>
     <t>LP</t>
   </si>
@@ -31,6 +31,9 @@
     <t>LP-051656</t>
   </si>
   <si>
+    <t>Encerrado!</t>
+  </si>
+  <si>
     <t>LP-051659</t>
   </si>
   <si>
@@ -62,9 +65,6 @@
   </si>
   <si>
     <t>LP-049891</t>
-  </si>
-  <si>
-    <t>LP-050304</t>
   </si>
   <si>
     <t>LP-050367</t>
@@ -535,12 +535,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -554,249 +550,280 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
         <v>50</v>
       </c>
     </row>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB29296-69C2-4EF9-8881-3AD34CD8C766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527D5B02-7FDC-4CCC-97F3-9598A9D6481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$22</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
   <si>
     <t>LP</t>
   </si>
@@ -28,96 +31,18 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-051369</t>
-  </si>
-  <si>
-    <t>LP-051388</t>
-  </si>
-  <si>
-    <t>LP-051391</t>
-  </si>
-  <si>
-    <t>LP-051395</t>
-  </si>
-  <si>
-    <t>LP-051425</t>
-  </si>
-  <si>
-    <t>LP-051431</t>
-  </si>
-  <si>
-    <t>LP-051432</t>
-  </si>
-  <si>
-    <t>LP-051434</t>
-  </si>
-  <si>
-    <t>LP-051448</t>
-  </si>
-  <si>
-    <t>LP-051449</t>
-  </si>
-  <si>
-    <t>LP-051519</t>
-  </si>
-  <si>
-    <t>LP-051540</t>
-  </si>
-  <si>
-    <t>LP-051541</t>
-  </si>
-  <si>
-    <t>LP-051543</t>
-  </si>
-  <si>
-    <t>LP-051705</t>
-  </si>
-  <si>
-    <t>LP-051712</t>
-  </si>
-  <si>
-    <t>LP-051716</t>
-  </si>
-  <si>
-    <t>LP-052122</t>
-  </si>
-  <si>
-    <t>LP-052138</t>
-  </si>
-  <si>
-    <t>LP-052141</t>
-  </si>
-  <si>
-    <t>LP-052160</t>
-  </si>
-  <si>
-    <t>LP-052199</t>
-  </si>
-  <si>
-    <t>LP-052308</t>
-  </si>
-  <si>
     <t>LP-052309</t>
   </si>
   <si>
+    <t>Compromisso pendente!</t>
+  </si>
+  <si>
     <t>LP-052311</t>
   </si>
   <si>
     <t>LP-052312</t>
   </si>
   <si>
-    <t>LP-052326</t>
-  </si>
-  <si>
-    <t>LP-052372</t>
-  </si>
-  <si>
-    <t>LP-052381</t>
-  </si>
-  <si>
-    <t>LP-052386</t>
-  </si>
-  <si>
     <t>LP-052400</t>
   </si>
   <si>
@@ -167,12 +92,6 @@
   </si>
   <si>
     <t>LP-052773</t>
-  </si>
-  <si>
-    <t>LP-052978</t>
-  </si>
-  <si>
-    <t>LP-053040</t>
   </si>
   <si>
     <t>LP-053105</t>
@@ -538,11 +457,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -557,250 +476,168 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>51</v>
+      <c r="B22" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs.xlsx
+++ b/08 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527D5B02-7FDC-4CCC-97F3-9598A9D6481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8171319F-F9C6-4360-9E01-B6EBA1F1D846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="106">
   <si>
     <t>LP</t>
   </si>
@@ -31,70 +31,316 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-052309</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-052311</t>
-  </si>
-  <si>
-    <t>LP-052312</t>
-  </si>
-  <si>
-    <t>LP-052400</t>
-  </si>
-  <si>
-    <t>LP-052406</t>
-  </si>
-  <si>
-    <t>LP-052623</t>
-  </si>
-  <si>
-    <t>LP-052680</t>
-  </si>
-  <si>
-    <t>LP-052681</t>
-  </si>
-  <si>
-    <t>LP-052720</t>
-  </si>
-  <si>
-    <t>LP-052721</t>
-  </si>
-  <si>
-    <t>LP-052722</t>
-  </si>
-  <si>
-    <t>LP-052726</t>
-  </si>
-  <si>
-    <t>LP-052727</t>
-  </si>
-  <si>
-    <t>LP-052728</t>
-  </si>
-  <si>
-    <t>LP-052729</t>
-  </si>
-  <si>
-    <t>LP-052749</t>
-  </si>
-  <si>
-    <t>LP-052752</t>
-  </si>
-  <si>
-    <t>LP-052754</t>
-  </si>
-  <si>
-    <t>LP-052756</t>
-  </si>
-  <si>
-    <t>LP-052773</t>
-  </si>
-  <si>
-    <t>LP-053105</t>
+    <t>LP-047527</t>
+  </si>
+  <si>
+    <t>LP-048805</t>
+  </si>
+  <si>
+    <t>LP-048964</t>
+  </si>
+  <si>
+    <t>LP-049027</t>
+  </si>
+  <si>
+    <t>LP-049395</t>
+  </si>
+  <si>
+    <t>LP-049396</t>
+  </si>
+  <si>
+    <t>LP-049460</t>
+  </si>
+  <si>
+    <t>LP-049943</t>
+  </si>
+  <si>
+    <t>LP-050090</t>
+  </si>
+  <si>
+    <t>LP-050470</t>
+  </si>
+  <si>
+    <t>LP-050669</t>
+  </si>
+  <si>
+    <t>LP-050684</t>
+  </si>
+  <si>
+    <t>LP-050740</t>
+  </si>
+  <si>
+    <t>LP-050980</t>
+  </si>
+  <si>
+    <t>LP-051044</t>
+  </si>
+  <si>
+    <t>LP-051051</t>
+  </si>
+  <si>
+    <t>LP-051096</t>
+  </si>
+  <si>
+    <t>LP-051218</t>
+  </si>
+  <si>
+    <t>LP-051299</t>
+  </si>
+  <si>
+    <t>LP-051303</t>
+  </si>
+  <si>
+    <t>LP-051304</t>
+  </si>
+  <si>
+    <t>LP-051348</t>
+  </si>
+  <si>
+    <t>LP-051389</t>
+  </si>
+  <si>
+    <t>LP-051427</t>
+  </si>
+  <si>
+    <t>LP-051512</t>
+  </si>
+  <si>
+    <t>LP-051521</t>
+  </si>
+  <si>
+    <t>LP-051523</t>
+  </si>
+  <si>
+    <t>LP-051535</t>
+  </si>
+  <si>
+    <t>LP-051707</t>
+  </si>
+  <si>
+    <t>LP-051726</t>
+  </si>
+  <si>
+    <t>LP-051727</t>
+  </si>
+  <si>
+    <t>LP-051810</t>
+  </si>
+  <si>
+    <t>LP-052013</t>
+  </si>
+  <si>
+    <t>LP-052015</t>
+  </si>
+  <si>
+    <t>LP-052116</t>
+  </si>
+  <si>
+    <t>LP-052161</t>
+  </si>
+  <si>
+    <t>LP-052306</t>
+  </si>
+  <si>
+    <t>LP-052310</t>
+  </si>
+  <si>
+    <t>LP-052396</t>
+  </si>
+  <si>
+    <t>LP-052625</t>
+  </si>
+  <si>
+    <t>LP-052714</t>
+  </si>
+  <si>
+    <t>LP-052723</t>
+  </si>
+  <si>
+    <t>LP-052746</t>
+  </si>
+  <si>
+    <t>LP-052788</t>
+  </si>
+  <si>
+    <t>LP-052789</t>
+  </si>
+  <si>
+    <t>LP-052901</t>
+  </si>
+  <si>
+    <t>LP-052976</t>
+  </si>
+  <si>
+    <t>LP-053081</t>
+  </si>
+  <si>
+    <t>LP-053082</t>
+  </si>
+  <si>
+    <t>LP-053240</t>
+  </si>
+  <si>
+    <t>LP-044473</t>
+  </si>
+  <si>
+    <t>LP-045731</t>
+  </si>
+  <si>
+    <t>LP-045881</t>
+  </si>
+  <si>
+    <t>LP-046622</t>
+  </si>
+  <si>
+    <t>LP-047092</t>
+  </si>
+  <si>
+    <t>LP-048363</t>
+  </si>
+  <si>
+    <t>LP-048642</t>
+  </si>
+  <si>
+    <t>LP-048660</t>
+  </si>
+  <si>
+    <t>LP-049444</t>
+  </si>
+  <si>
+    <t>LP-050458</t>
+  </si>
+  <si>
+    <t>LP-050906</t>
+  </si>
+  <si>
+    <t>LP-051037</t>
+  </si>
+  <si>
+    <t>LP-051053</t>
+  </si>
+  <si>
+    <t>LP-051216</t>
+  </si>
+  <si>
+    <t>LP-051411</t>
+  </si>
+  <si>
+    <t>LP-051429</t>
+  </si>
+  <si>
+    <t>LP-051439</t>
+  </si>
+  <si>
+    <t>LP-051600</t>
+  </si>
+  <si>
+    <t>LP-051751</t>
+  </si>
+  <si>
+    <t>LP-051991</t>
+  </si>
+  <si>
+    <t>LP-051993</t>
+  </si>
+  <si>
+    <t>LP-051995</t>
+  </si>
+  <si>
+    <t>LP-051998</t>
+  </si>
+  <si>
+    <t>LP-052204</t>
+  </si>
+  <si>
+    <t>LP-052256</t>
+  </si>
+  <si>
+    <t>LP-052302</t>
+  </si>
+  <si>
+    <t>LP-052303</t>
+  </si>
+  <si>
+    <t>LP-052322</t>
+  </si>
+  <si>
+    <t>LP-052353</t>
+  </si>
+  <si>
+    <t>LP-052356</t>
+  </si>
+  <si>
+    <t>LP-052357</t>
+  </si>
+  <si>
+    <t>LP-052361</t>
+  </si>
+  <si>
+    <t>LP-052412</t>
+  </si>
+  <si>
+    <t>LP-052414</t>
+  </si>
+  <si>
+    <t>LP-052424</t>
+  </si>
+  <si>
+    <t>LP-052495</t>
+  </si>
+  <si>
+    <t>LP-052496</t>
+  </si>
+  <si>
+    <t>LP-052497</t>
+  </si>
+  <si>
+    <t>LP-052498</t>
+  </si>
+  <si>
+    <t>LP-052499</t>
+  </si>
+  <si>
+    <t>LP-052506</t>
+  </si>
+  <si>
+    <t>LP-052636</t>
+  </si>
+  <si>
+    <t>LP-052767</t>
+  </si>
+  <si>
+    <t>LP-051780</t>
+  </si>
+  <si>
+    <t>LP-052848</t>
+  </si>
+  <si>
+    <t>LP-052929</t>
+  </si>
+  <si>
+    <t>LP-053136</t>
+  </si>
+  <si>
+    <t>LP-053175</t>
+  </si>
+  <si>
+    <t>LP-053456</t>
+  </si>
+  <si>
+    <t>LP-053483</t>
+  </si>
+  <si>
+    <t>LP-053542</t>
+  </si>
+  <si>
+    <t>LP-053544</t>
+  </si>
+  <si>
+    <t>LP-053610</t>
+  </si>
+  <si>
+    <t>LP-121985</t>
   </si>
 </sst>
 </file>
@@ -457,11 +703,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -476,168 +722,535 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B22" t="s">
-        <v>3</v>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
